--- a/dist/downloads/精品货价监控指标_Sheet1.xlsx
+++ b/dist/downloads/精品货价监控指标_Sheet1.xlsx
@@ -9,7 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1" forceFullCalc="1"/>
+  <calcPr calcId="191029" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="C1" s="11" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="D1" s="11" t="inlineStr">
         <is>
@@ -1845,28 +1845,28 @@
         <v>71810000</v>
       </c>
       <c r="D6" s="103" t="n">
-        <v>32389627.70686</v>
+        <v>34975149.62313001</v>
       </c>
       <c r="E6" s="104">
         <f>D6/C6</f>
         <v/>
       </c>
       <c r="F6" s="103" t="n">
-        <v>31643223.77757</v>
+        <v>33850963.58139</v>
       </c>
       <c r="G6" s="104">
         <f>D6/F6-1</f>
         <v/>
       </c>
       <c r="H6" s="103" t="n">
-        <v>35522514.17281207</v>
+        <v>38086530.63278449</v>
       </c>
       <c r="I6" s="104">
         <f>D6/H6</f>
         <v/>
       </c>
       <c r="J6" s="103" t="n">
-        <v>35000000</v>
+        <v>37100000</v>
       </c>
       <c r="K6" s="104">
         <f>D6/J6</f>
@@ -1884,28 +1884,28 @@
         <v>132000000</v>
       </c>
       <c r="D7" s="103" t="n">
-        <v>46036869.25590001</v>
+        <v>49619233.40631</v>
       </c>
       <c r="E7" s="104">
         <f>D7/C7</f>
         <v/>
       </c>
       <c r="F7" s="103" t="n">
-        <v>53288833.82045999</v>
+        <v>56687345.14430998</v>
       </c>
       <c r="G7" s="104">
         <f>D7/F7-1</f>
         <v/>
       </c>
       <c r="H7" s="103" t="n">
-        <v>65296920.63516492</v>
+        <v>70010054.9161336</v>
       </c>
       <c r="I7" s="104">
         <f>D7/H7</f>
         <v/>
       </c>
       <c r="J7" s="103" t="n">
-        <v>66844327.6</v>
+        <v>71106215.3</v>
       </c>
       <c r="K7" s="104">
         <f>D7/J7</f>
@@ -1923,28 +1923,28 @@
         <v>9437018</v>
       </c>
       <c r="D8" s="103" t="n">
-        <v>5911715.114849999</v>
+        <v>6210733.969369999</v>
       </c>
       <c r="E8" s="104">
         <f>D8/C8</f>
         <v/>
       </c>
       <c r="F8" s="103" t="n">
-        <v>3735617.23936</v>
+        <v>3953414.42998</v>
       </c>
       <c r="G8" s="104">
         <f>D8/F8-1</f>
         <v/>
       </c>
       <c r="H8" s="103" t="n">
-        <v>4668244.055898658</v>
+        <v>5005198.094125312</v>
       </c>
       <c r="I8" s="104">
         <f>D8/H8</f>
         <v/>
       </c>
       <c r="J8" s="103" t="n">
-        <v>4807018.15389968</v>
+        <v>5067018.15389968</v>
       </c>
       <c r="K8" s="104">
         <f>D8/J8</f>
@@ -1962,28 +1962,28 @@
         <v>88000000</v>
       </c>
       <c r="D9" s="103" t="n">
-        <v>38550501.94708</v>
+        <v>40986570.86557</v>
       </c>
       <c r="E9" s="104">
         <f>D9/C9</f>
         <v/>
       </c>
       <c r="F9" s="103" t="n">
-        <v>36103787.69422</v>
+        <v>39410895.44554999</v>
       </c>
       <c r="G9" s="104">
         <f>D9/F9-1</f>
         <v/>
       </c>
       <c r="H9" s="103" t="n">
-        <v>43531280.42344328</v>
+        <v>46673369.94408906</v>
       </c>
       <c r="I9" s="104">
         <f>D9/H9</f>
         <v/>
       </c>
       <c r="J9" s="103" t="n">
-        <v>42022350</v>
+        <v>46808785</v>
       </c>
       <c r="K9" s="104">
         <f>D9/J9</f>
@@ -2001,28 +2001,28 @@
         <v>66000000</v>
       </c>
       <c r="D10" s="103" t="n">
-        <v>29962467.94621</v>
+        <v>31610855.76639</v>
       </c>
       <c r="E10" s="104">
         <f>D10/C10</f>
         <v/>
       </c>
       <c r="F10" s="103" t="n">
-        <v>29040917.19023</v>
+        <v>31381136.05132</v>
       </c>
       <c r="G10" s="104">
         <f>D10/F10-1</f>
         <v/>
       </c>
       <c r="H10" s="103" t="n">
-        <v>32648460.31758246</v>
+        <v>35005027.4580668</v>
       </c>
       <c r="I10" s="104">
         <f>D10/H10</f>
         <v/>
       </c>
       <c r="J10" s="103" t="n">
-        <v>34200000</v>
+        <v>36200000</v>
       </c>
       <c r="K10" s="104">
         <f>D10/J10</f>
@@ -2040,28 +2040,28 @@
         <v>62390797</v>
       </c>
       <c r="D11" s="103" t="n">
-        <v>22614057.90135</v>
+        <v>24159296.11852</v>
       </c>
       <c r="E11" s="104">
         <f>D11/C11</f>
         <v/>
       </c>
       <c r="F11" s="103" t="n">
-        <v>26008759.14053</v>
+        <v>27740624.68211</v>
       </c>
       <c r="G11" s="104">
         <f>D11/F11-1</f>
         <v/>
       </c>
       <c r="H11" s="103" t="n">
-        <v>30863082.72783095</v>
+        <v>33090781.24417684</v>
       </c>
       <c r="I11" s="104">
         <f>D11/H11</f>
         <v/>
       </c>
       <c r="J11" s="103" t="n">
-        <v>31258269.39</v>
+        <v>33171057.52</v>
       </c>
       <c r="K11" s="104">
         <f>D11/J11</f>
@@ -3943,40 +3943,40 @@
         </is>
       </c>
       <c r="C46" s="107" t="n">
-        <v>97.93021553000001</v>
+        <v>107.60307687</v>
       </c>
       <c r="D46" s="108" t="n">
-        <v>100.814</v>
+        <v>110.766</v>
       </c>
       <c r="E46" s="108" t="n">
         <v>0</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>0.971395</v>
+        <v>0.971445</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>0.028605</v>
+        <v>0.028555</v>
       </c>
       <c r="H46" s="104" t="n">
-        <v>0.793439</v>
+        <v>0.792044</v>
       </c>
       <c r="I46" s="104" t="n">
-        <v>0.813846</v>
+        <v>0.817427</v>
       </c>
       <c r="J46" s="14" t="n">
-        <v>-2.0407</v>
+        <v>-2.5383</v>
       </c>
       <c r="K46" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L46" s="104" t="n">
-        <v>0.985509</v>
+        <v>0.98561</v>
       </c>
       <c r="M46" s="104" t="n">
-        <v>0.844546</v>
+        <v>0.848127</v>
       </c>
       <c r="N46" s="14" t="n">
-        <v>14.0963</v>
+        <v>13.74830000000001</v>
       </c>
       <c r="O46" s="14" t="n">
         <v>-2</v>
@@ -3999,31 +3999,31 @@
         <v>0</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>0.545478</v>
+        <v>0.536247</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>0.454522</v>
+        <v>0.463753</v>
       </c>
       <c r="H47" s="104" t="n">
-        <v>0.871382</v>
+        <v>0.8682609999999999</v>
       </c>
       <c r="I47" s="104" t="n">
-        <v>0.855704</v>
+        <v>0.854326</v>
       </c>
       <c r="J47" s="14" t="n">
-        <v>1.5678</v>
+        <v>1.3935</v>
       </c>
       <c r="K47" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L47" s="104" t="n">
-        <v>0.949881</v>
+        <v>0.951398</v>
       </c>
       <c r="M47" s="104" t="n">
-        <v>0.886404</v>
+        <v>0.8850259999999999</v>
       </c>
       <c r="N47" s="14" t="n">
-        <v>6.347700000000003</v>
+        <v>6.637200000000007</v>
       </c>
       <c r="O47" s="14" t="n">
         <v>-2</v>
@@ -4037,40 +4037,40 @@
         </is>
       </c>
       <c r="C48" s="107" t="n">
-        <v>109.59882038</v>
+        <v>104.976746898</v>
       </c>
       <c r="D48" s="108" t="n">
-        <v>108.652</v>
+        <v>103.594</v>
       </c>
       <c r="E48" s="108" t="n">
         <v>120</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>0.916565</v>
+        <v>0.915717</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>0.083435</v>
+        <v>0.084283</v>
       </c>
       <c r="H48" s="104" t="n">
-        <v>0.756123</v>
+        <v>0.755937</v>
       </c>
       <c r="I48" s="104" t="n">
-        <v>0.7804489999999999</v>
+        <v>0.777734</v>
       </c>
       <c r="J48" s="14" t="n">
-        <v>-2.4326</v>
+        <v>-2.1797</v>
       </c>
       <c r="K48" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L48" s="104" t="n">
-        <v>0.75467</v>
+        <v>0.751426</v>
       </c>
       <c r="M48" s="104" t="n">
-        <v>0.8111489999999999</v>
+        <v>0.8084339999999999</v>
       </c>
       <c r="N48" s="14" t="n">
-        <v>-5.647899999999993</v>
+        <v>-5.700799999999987</v>
       </c>
       <c r="O48" s="14" t="n">
         <v>-2</v>
@@ -4084,40 +4084,40 @@
         </is>
       </c>
       <c r="C49" s="107" t="n">
-        <v>78.824133768</v>
+        <v>82.429839468</v>
       </c>
       <c r="D49" s="108" t="n">
-        <v>90.294</v>
+        <v>94.422</v>
       </c>
       <c r="E49" s="108" t="n">
         <v>0</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>0.872972</v>
+        <v>0.872994</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>0.127028</v>
+        <v>0.127006</v>
       </c>
       <c r="H49" s="104" t="n">
-        <v>0.811846</v>
+        <v>0.810068</v>
       </c>
       <c r="I49" s="104" t="n">
-        <v>0.826993</v>
+        <v>0.827279</v>
       </c>
       <c r="J49" s="14" t="n">
-        <v>-1.5147</v>
+        <v>-1.7211</v>
       </c>
       <c r="K49" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L49" s="104" t="n">
-        <v>0.873203</v>
+        <v>0.870824</v>
       </c>
       <c r="M49" s="104" t="n">
-        <v>0.8576929999999998</v>
+        <v>0.8579789999999999</v>
       </c>
       <c r="N49" s="14" t="n">
-        <v>1.551000000000016</v>
+        <v>1.284500000000008</v>
       </c>
       <c r="O49" s="14" t="n">
         <v>-2</v>
@@ -4140,31 +4140,31 @@
         <v>0</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>0.820505</v>
+        <v>0.820496</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>0.179495</v>
+        <v>0.179504</v>
       </c>
       <c r="H50" s="104" t="n">
-        <v>0.884324</v>
+        <v>0.883811</v>
       </c>
       <c r="I50" s="104" t="n">
-        <v>0.831376</v>
+        <v>0.832088</v>
       </c>
       <c r="J50" s="14" t="n">
-        <v>5.2948</v>
+        <v>5.1723</v>
       </c>
       <c r="K50" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L50" s="104" t="n">
-        <v>0.887052</v>
+        <v>0.887315</v>
       </c>
       <c r="M50" s="104" t="n">
-        <v>0.862076</v>
+        <v>0.8627879999999999</v>
       </c>
       <c r="N50" s="14" t="n">
-        <v>2.497600000000006</v>
+        <v>2.452700000000007</v>
       </c>
       <c r="O50" s="14" t="n">
         <v>-2</v>
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="C69" s="10" t="n">
-        <v>0.9442551200979122</v>
+        <v>0.9427468344236526</v>
       </c>
       <c r="D69" s="10" t="n">
-        <v>0.9351252719748095</v>
+        <v>0.9332225462432315</v>
       </c>
       <c r="E69" s="10">
         <f>D69-C69</f>
@@ -6886,10 +6886,10 @@
         </is>
       </c>
       <c r="C70" s="10" t="n">
-        <v>0.9385070529208377</v>
+        <v>0.9372843585708187</v>
       </c>
       <c r="D70" s="10" t="n">
-        <v>0.8904571310876348</v>
+        <v>0.8898607515239287</v>
       </c>
       <c r="E70" s="10">
         <f>D70-C70</f>
@@ -6975,10 +6975,10 @@
         </is>
       </c>
       <c r="C71" s="10" t="n">
-        <v>0.933685712972067</v>
+        <v>0.9320403064061903</v>
       </c>
       <c r="D71" s="10" t="n">
-        <v>0.8888831732323637</v>
+        <v>0.8883333799460382</v>
       </c>
       <c r="E71" s="10">
         <f>D71-C71</f>
@@ -7064,10 +7064,10 @@
         </is>
       </c>
       <c r="C72" s="10" t="n">
-        <v>0.9779898468577517</v>
+        <v>0.9772636330854493</v>
       </c>
       <c r="D72" s="10" t="n">
-        <v>0.8722023115804697</v>
+        <v>0.872594288391489</v>
       </c>
       <c r="E72" s="10">
         <f>D72-C72</f>
@@ -7153,10 +7153,10 @@
         </is>
       </c>
       <c r="C73" s="10" t="n">
-        <v>0.962906447794792</v>
+        <v>0.9577927280300074</v>
       </c>
       <c r="D73" s="10" t="n">
-        <v>0.8449899596660958</v>
+        <v>0.8426085357633553</v>
       </c>
       <c r="E73" s="10">
         <f>D73-C73</f>
@@ -7242,10 +7242,10 @@
         </is>
       </c>
       <c r="C74" s="10" t="n">
-        <v>0.9475576301941477</v>
+        <v>0.945974185455224</v>
       </c>
       <c r="D74" s="10" t="n">
-        <v>0.8800287196118829</v>
+        <v>0.8788971925389848</v>
       </c>
       <c r="E74" s="10">
         <f>D74-C74</f>
@@ -7331,10 +7331,10 @@
         </is>
       </c>
       <c r="C75" s="10" t="n">
-        <v>0.9430572607356902</v>
+        <v>0.9416109877180318</v>
       </c>
       <c r="D75" s="10" t="n">
-        <v>0.8852997933328283</v>
+        <v>0.8845619506364751</v>
       </c>
       <c r="E75" s="10">
         <f>D75-C75</f>
@@ -10779,10 +10779,10 @@
         </is>
       </c>
       <c r="C149" s="116" t="n">
-        <v>0.2109305926466908</v>
+        <v>0.2100804882819329</v>
       </c>
       <c r="D149" s="116" t="n">
-        <v>0.333069</v>
+        <v>0.335974</v>
       </c>
       <c r="E149" s="20">
         <f>D149/C149</f>
@@ -10800,10 +10800,10 @@
         <v/>
       </c>
       <c r="I149" s="106" t="n">
-        <v>7848911.466666667</v>
+        <v>7788367.25</v>
       </c>
       <c r="J149" s="106" t="n">
-        <v>1469871.58898</v>
+        <v>1487982.675145</v>
       </c>
       <c r="K149" s="13" t="inlineStr">
         <is>
@@ -10818,10 +10818,10 @@
         </is>
       </c>
       <c r="C150" s="116" t="n">
-        <v>0.006752232719069173</v>
+        <v>0.00677195226220127</v>
       </c>
       <c r="D150" s="116" t="n">
-        <v>0.02843437961289845</v>
+        <v>0.02880624824907791</v>
       </c>
       <c r="E150" s="20">
         <f>D150/C150</f>
@@ -10839,10 +10839,10 @@
         <v/>
       </c>
       <c r="I150" s="106" t="n">
-        <v>5270625</v>
+        <v>5621606</v>
       </c>
       <c r="J150" s="106" t="n">
-        <v>2725288.33066</v>
+        <v>2962708.56432</v>
       </c>
     </row>
     <row r="152" ht="13.5" customHeight="1">

--- a/dist/downloads/精品货价监控指标_Sheet1.xlsx
+++ b/dist/downloads/精品货价监控指标_Sheet1.xlsx
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="C1" s="11" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="D1" s="11" t="inlineStr">
         <is>
@@ -1845,28 +1845,28 @@
         <v>71810000</v>
       </c>
       <c r="D6" s="103" t="n">
-        <v>34975149.62313001</v>
+        <v>41171977.66142999</v>
       </c>
       <c r="E6" s="104">
         <f>D6/C6</f>
         <v/>
       </c>
       <c r="F6" s="103" t="n">
-        <v>33850963.58139</v>
+        <v>39870920.72767</v>
       </c>
       <c r="G6" s="104">
         <f>D6/F6-1</f>
         <v/>
       </c>
       <c r="H6" s="103" t="n">
-        <v>38086530.63278449</v>
+        <v>44282217.04154427</v>
       </c>
       <c r="I6" s="104">
         <f>D6/H6</f>
         <v/>
       </c>
       <c r="J6" s="103" t="n">
-        <v>37100000</v>
+        <v>44600000</v>
       </c>
       <c r="K6" s="104">
         <f>D6/J6</f>
@@ -1884,28 +1884,28 @@
         <v>132000000</v>
       </c>
       <c r="D7" s="103" t="n">
-        <v>49619233.40631</v>
+        <v>58418083.24780001</v>
       </c>
       <c r="E7" s="104">
         <f>D7/C7</f>
         <v/>
       </c>
       <c r="F7" s="103" t="n">
-        <v>56687345.14430998</v>
+        <v>65883708.92365</v>
       </c>
       <c r="G7" s="104">
         <f>D7/F7-1</f>
         <v/>
       </c>
       <c r="H7" s="103" t="n">
-        <v>70010054.9161336</v>
+        <v>81398867.14223428</v>
       </c>
       <c r="I7" s="104">
         <f>D7/H7</f>
         <v/>
       </c>
       <c r="J7" s="103" t="n">
-        <v>71106215.3</v>
+        <v>82641342.7</v>
       </c>
       <c r="K7" s="104">
         <f>D7/J7</f>
@@ -1923,28 +1923,28 @@
         <v>9437018</v>
       </c>
       <c r="D8" s="103" t="n">
-        <v>6210733.969369999</v>
+        <v>7043379.949359999</v>
       </c>
       <c r="E8" s="104">
         <f>D8/C8</f>
         <v/>
       </c>
       <c r="F8" s="103" t="n">
-        <v>3953414.42998</v>
+        <v>4519848.26041</v>
       </c>
       <c r="G8" s="104">
         <f>D8/F8-1</f>
         <v/>
       </c>
       <c r="H8" s="103" t="n">
-        <v>5005198.094125312</v>
+        <v>5819413.442430859</v>
       </c>
       <c r="I8" s="104">
         <f>D8/H8</f>
         <v/>
       </c>
       <c r="J8" s="103" t="n">
-        <v>5067018.15389968</v>
+        <v>5847018.15389968</v>
       </c>
       <c r="K8" s="104">
         <f>D8/J8</f>
@@ -1962,28 +1962,28 @@
         <v>88000000</v>
       </c>
       <c r="D9" s="103" t="n">
-        <v>40986570.86557</v>
+        <v>50217161.58193</v>
       </c>
       <c r="E9" s="104">
         <f>D9/C9</f>
         <v/>
       </c>
       <c r="F9" s="103" t="n">
-        <v>39410895.44554999</v>
+        <v>45786525.72287001</v>
       </c>
       <c r="G9" s="104">
         <f>D9/F9-1</f>
         <v/>
       </c>
       <c r="H9" s="103" t="n">
-        <v>46673369.94408906</v>
+        <v>54265911.42815619</v>
       </c>
       <c r="I9" s="104">
         <f>D9/H9</f>
         <v/>
       </c>
       <c r="J9" s="103" t="n">
-        <v>46808785</v>
+        <v>54575872</v>
       </c>
       <c r="K9" s="104">
         <f>D9/J9</f>
@@ -2001,28 +2001,28 @@
         <v>66000000</v>
       </c>
       <c r="D10" s="103" t="n">
-        <v>31610855.76639</v>
+        <v>37166308.61001</v>
       </c>
       <c r="E10" s="104">
         <f>D10/C10</f>
         <v/>
       </c>
       <c r="F10" s="103" t="n">
-        <v>31381136.05132</v>
+        <v>35875548.66118</v>
       </c>
       <c r="G10" s="104">
         <f>D10/F10-1</f>
         <v/>
       </c>
       <c r="H10" s="103" t="n">
-        <v>35005027.4580668</v>
+        <v>40699433.57111714</v>
       </c>
       <c r="I10" s="104">
         <f>D10/H10</f>
         <v/>
       </c>
       <c r="J10" s="103" t="n">
-        <v>36200000</v>
+        <v>41800000</v>
       </c>
       <c r="K10" s="104">
         <f>D10/J10</f>
@@ -2040,28 +2040,28 @@
         <v>62390797</v>
       </c>
       <c r="D11" s="103" t="n">
-        <v>24159296.11852</v>
+        <v>29036981.66141</v>
       </c>
       <c r="E11" s="104">
         <f>D11/C11</f>
         <v/>
       </c>
       <c r="F11" s="103" t="n">
-        <v>27740624.68211</v>
+        <v>32989934.38993</v>
       </c>
       <c r="G11" s="104">
         <f>D11/F11-1</f>
         <v/>
       </c>
       <c r="H11" s="103" t="n">
-        <v>33090781.24417684</v>
+        <v>38473789.36288719</v>
       </c>
       <c r="I11" s="104">
         <f>D11/H11</f>
         <v/>
       </c>
       <c r="J11" s="103" t="n">
-        <v>33171057.52</v>
+        <v>40002249.98</v>
       </c>
       <c r="K11" s="104">
         <f>D11/J11</f>
@@ -3943,40 +3943,40 @@
         </is>
       </c>
       <c r="C46" s="107" t="n">
-        <v>107.60307687</v>
+        <v>116.46168</v>
       </c>
       <c r="D46" s="108" t="n">
-        <v>110.766</v>
+        <v>120</v>
       </c>
       <c r="E46" s="108" t="n">
         <v>0</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>0.971445</v>
+        <v>0.970514</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>0.028555</v>
+        <v>0.029486</v>
       </c>
       <c r="H46" s="104" t="n">
-        <v>0.792044</v>
+        <v>0.792861</v>
       </c>
       <c r="I46" s="104" t="n">
-        <v>0.817427</v>
+        <v>0.823144</v>
       </c>
       <c r="J46" s="14" t="n">
-        <v>-2.5383</v>
+        <v>-3.0283</v>
       </c>
       <c r="K46" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L46" s="104" t="n">
-        <v>0.98561</v>
+        <v>0.980118</v>
       </c>
       <c r="M46" s="104" t="n">
-        <v>0.848127</v>
+        <v>0.853844</v>
       </c>
       <c r="N46" s="14" t="n">
-        <v>13.74830000000001</v>
+        <v>12.62739999999999</v>
       </c>
       <c r="O46" s="14" t="n">
         <v>-2</v>
@@ -3999,31 +3999,31 @@
         <v>0</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>0.536247</v>
+        <v>0.547494</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>0.463753</v>
+        <v>0.452506</v>
       </c>
       <c r="H47" s="104" t="n">
-        <v>0.8682609999999999</v>
+        <v>0.851843</v>
       </c>
       <c r="I47" s="104" t="n">
-        <v>0.854326</v>
+        <v>0.849729</v>
       </c>
       <c r="J47" s="14" t="n">
-        <v>1.3935</v>
+        <v>0.2114</v>
       </c>
       <c r="K47" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L47" s="104" t="n">
-        <v>0.951398</v>
+        <v>0.951146</v>
       </c>
       <c r="M47" s="104" t="n">
-        <v>0.8850259999999999</v>
+        <v>0.8804289999999999</v>
       </c>
       <c r="N47" s="14" t="n">
-        <v>6.637200000000007</v>
+        <v>7.071700000000007</v>
       </c>
       <c r="O47" s="14" t="n">
         <v>-2</v>
@@ -4037,40 +4037,40 @@
         </is>
       </c>
       <c r="C48" s="107" t="n">
-        <v>104.976746898</v>
+        <v>97.47265964</v>
       </c>
       <c r="D48" s="108" t="n">
-        <v>103.594</v>
+        <v>95.402</v>
       </c>
       <c r="E48" s="108" t="n">
         <v>120</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>0.915717</v>
+        <v>0.91582</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>0.084283</v>
+        <v>0.08418</v>
       </c>
       <c r="H48" s="104" t="n">
-        <v>0.755937</v>
+        <v>0.757598</v>
       </c>
       <c r="I48" s="104" t="n">
-        <v>0.777734</v>
+        <v>0.775299</v>
       </c>
       <c r="J48" s="14" t="n">
-        <v>-2.1797</v>
+        <v>-1.7701</v>
       </c>
       <c r="K48" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L48" s="104" t="n">
-        <v>0.751426</v>
+        <v>0.74193</v>
       </c>
       <c r="M48" s="104" t="n">
-        <v>0.8084339999999999</v>
+        <v>0.8059989999999999</v>
       </c>
       <c r="N48" s="14" t="n">
-        <v>-5.700799999999987</v>
+        <v>-6.406899999999993</v>
       </c>
       <c r="O48" s="14" t="n">
         <v>-2</v>
@@ -4084,40 +4084,40 @@
         </is>
       </c>
       <c r="C49" s="107" t="n">
-        <v>82.429839468</v>
+        <v>89.49326068799999</v>
       </c>
       <c r="D49" s="108" t="n">
-        <v>94.422</v>
+        <v>102.616</v>
       </c>
       <c r="E49" s="108" t="n">
         <v>0</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>0.872994</v>
+        <v>0.8721179999999999</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>0.127006</v>
+        <v>0.127882</v>
       </c>
       <c r="H49" s="104" t="n">
-        <v>0.810068</v>
+        <v>0.80793</v>
       </c>
       <c r="I49" s="104" t="n">
-        <v>0.827279</v>
+        <v>0.829238</v>
       </c>
       <c r="J49" s="14" t="n">
-        <v>-1.7211</v>
+        <v>-2.1308</v>
       </c>
       <c r="K49" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L49" s="104" t="n">
-        <v>0.870824</v>
+        <v>0.87088</v>
       </c>
       <c r="M49" s="104" t="n">
-        <v>0.8579789999999999</v>
+        <v>0.859938</v>
       </c>
       <c r="N49" s="14" t="n">
-        <v>1.284500000000008</v>
+        <v>1.094200000000001</v>
       </c>
       <c r="O49" s="14" t="n">
         <v>-2</v>
@@ -4140,31 +4140,31 @@
         <v>0</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>0.820496</v>
+        <v>0.820179</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>0.179504</v>
+        <v>0.179821</v>
       </c>
       <c r="H50" s="104" t="n">
-        <v>0.883811</v>
+        <v>0.886393</v>
       </c>
       <c r="I50" s="104" t="n">
-        <v>0.832088</v>
+        <v>0.835625</v>
       </c>
       <c r="J50" s="14" t="n">
-        <v>5.1723</v>
+        <v>5.0768</v>
       </c>
       <c r="K50" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L50" s="104" t="n">
-        <v>0.887315</v>
+        <v>0.887994</v>
       </c>
       <c r="M50" s="104" t="n">
-        <v>0.8627879999999999</v>
+        <v>0.8663249999999999</v>
       </c>
       <c r="N50" s="14" t="n">
-        <v>2.452700000000007</v>
+        <v>2.166900000000012</v>
       </c>
       <c r="O50" s="14" t="n">
         <v>-2</v>
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="C69" s="10" t="n">
-        <v>0.9427468344236526</v>
+        <v>0.9391932047017469</v>
       </c>
       <c r="D69" s="10" t="n">
-        <v>0.9332225462432315</v>
+        <v>0.9300424722153577</v>
       </c>
       <c r="E69" s="10">
         <f>D69-C69</f>
@@ -6886,10 +6886,10 @@
         </is>
       </c>
       <c r="C70" s="10" t="n">
-        <v>0.9372843585708187</v>
+        <v>0.9342072505209006</v>
       </c>
       <c r="D70" s="10" t="n">
-        <v>0.8898607515239287</v>
+        <v>0.8890427547929984</v>
       </c>
       <c r="E70" s="10">
         <f>D70-C70</f>
@@ -6975,10 +6975,10 @@
         </is>
       </c>
       <c r="C71" s="10" t="n">
-        <v>0.9320403064061903</v>
+        <v>0.9281154743709659</v>
       </c>
       <c r="D71" s="10" t="n">
-        <v>0.8883333799460382</v>
+        <v>0.8884953019252709</v>
       </c>
       <c r="E71" s="10">
         <f>D71-C71</f>
@@ -7064,10 +7064,10 @@
         </is>
       </c>
       <c r="C72" s="10" t="n">
-        <v>0.9772636330854493</v>
+        <v>0.974922644430219</v>
       </c>
       <c r="D72" s="10" t="n">
-        <v>0.872594288391489</v>
+        <v>0.8723162364702726</v>
       </c>
       <c r="E72" s="10">
         <f>D72-C72</f>
@@ -7153,10 +7153,10 @@
         </is>
       </c>
       <c r="C73" s="10" t="n">
-        <v>0.9577927280300074</v>
+        <v>0.9457953338027764</v>
       </c>
       <c r="D73" s="10" t="n">
-        <v>0.8426085357633553</v>
+        <v>0.8367295224048984</v>
       </c>
       <c r="E73" s="10">
         <f>D73-C73</f>
@@ -7242,10 +7242,10 @@
         </is>
       </c>
       <c r="C74" s="10" t="n">
-        <v>0.945974185455224</v>
+        <v>0.9421029888053504</v>
       </c>
       <c r="D74" s="10" t="n">
-        <v>0.8788971925389848</v>
+        <v>0.879677870232397</v>
       </c>
       <c r="E74" s="10">
         <f>D74-C74</f>
@@ -7331,10 +7331,10 @@
         </is>
       </c>
       <c r="C75" s="10" t="n">
-        <v>0.9416109877180318</v>
+        <v>0.9380595280669098</v>
       </c>
       <c r="D75" s="10" t="n">
-        <v>0.8845619506364751</v>
+        <v>0.884070603110812</v>
       </c>
       <c r="E75" s="10">
         <f>D75-C75</f>
@@ -7517,13 +7517,13 @@
         </is>
       </c>
       <c r="C81" s="18" t="n">
-        <v>1426.133333333333</v>
+        <v>1417.578947368421</v>
       </c>
       <c r="D81" s="104" t="n">
-        <v>0.7102655198204936</v>
+        <v>0.7105145912229895</v>
       </c>
       <c r="E81" s="104" t="n">
-        <v>0.894085</v>
+        <v>0.89395</v>
       </c>
       <c r="F81" s="104" t="n">
         <v>0.8146325152</v>
@@ -7533,7 +7533,7 @@
         <v/>
       </c>
       <c r="H81" s="104" t="n">
-        <v>0.885304</v>
+        <v>0.8848</v>
       </c>
       <c r="I81" s="104" t="n">
         <v>0.8207995184</v>
@@ -7543,7 +7543,7 @@
         <v/>
       </c>
       <c r="K81" s="104" t="n">
-        <v>0.7725321888412017</v>
+        <v>0.8059210526315789</v>
       </c>
       <c r="L81" s="104" t="n">
         <v>0.8082191781</v>
@@ -7553,7 +7553,7 @@
         <v/>
       </c>
       <c r="N81" s="104" t="n">
-        <v>0.0674717790657853</v>
+        <v>0.0712106478980485</v>
       </c>
       <c r="O81" s="104" t="n">
         <v>0.0611152139</v>
@@ -7570,13 +7570,13 @@
         </is>
       </c>
       <c r="C82" s="18" t="n">
-        <v>113.6</v>
+        <v>115.4736842105263</v>
       </c>
       <c r="D82" s="104" t="n">
-        <v>0.2488262910798122</v>
+        <v>0.2525068368277119</v>
       </c>
       <c r="E82" s="104" t="n">
-        <v>0.726978</v>
+        <v>0.729419</v>
       </c>
       <c r="F82" s="104" t="n">
         <v>0.7556221149</v>
@@ -7608,7 +7608,7 @@
         <v/>
       </c>
       <c r="N82" s="104" t="n">
-        <v>0.1528878822197055</v>
+        <v>0.1462979482604817</v>
       </c>
       <c r="O82" s="104" t="n">
         <v>0.0611152139</v>
@@ -7625,13 +7625,13 @@
         </is>
       </c>
       <c r="C83" s="18" t="n">
-        <v>333</v>
+        <v>323.9473684210527</v>
       </c>
       <c r="D83" s="104" t="n">
-        <v>0.7187187187187187</v>
+        <v>0.7166531275385865</v>
       </c>
       <c r="E83" s="104" t="n">
-        <v>0.885275</v>
+        <v>0.884624</v>
       </c>
       <c r="F83" s="104" t="n">
         <v>0.8066</v>
@@ -7641,7 +7641,7 @@
         <v/>
       </c>
       <c r="H83" s="104" t="n">
-        <v>0.884537</v>
+        <v>0.8840479999999999</v>
       </c>
       <c r="I83" s="104" t="n">
         <v>0.8207995184</v>
@@ -7651,7 +7651,7 @@
         <v/>
       </c>
       <c r="K83" s="104" t="n">
-        <v>1</v>
+        <v>0.9375</v>
       </c>
       <c r="L83" s="104" t="n">
         <v>0.8082191781</v>
@@ -7661,7 +7661,7 @@
         <v/>
       </c>
       <c r="N83" s="104" t="n">
-        <v>0.056609623015873</v>
+        <v>0.0537193203272498</v>
       </c>
       <c r="O83" s="104" t="n">
         <v>0.0611152139</v>
@@ -7678,13 +7678,13 @@
         </is>
       </c>
       <c r="C84" s="18" t="n">
-        <v>881.2</v>
+        <v>879.578947368421</v>
       </c>
       <c r="D84" s="104" t="n">
-        <v>0.8033741867150855</v>
+        <v>0.804571565342269</v>
       </c>
       <c r="E84" s="104" t="n">
-        <v>0.911267</v>
+        <v>0.912312</v>
       </c>
       <c r="F84" s="104" t="n">
         <v>0.8078</v>
@@ -7694,7 +7694,7 @@
         <v/>
       </c>
       <c r="H84" s="104" t="n">
-        <v>0.890388</v>
+        <v>0.890002</v>
       </c>
       <c r="I84" s="104" t="n">
         <v>0.8207995184</v>
@@ -7704,7 +7704,7 @@
         <v/>
       </c>
       <c r="K84" s="104" t="n">
-        <v>0.7346938775510204</v>
+        <v>0.7831325301204819</v>
       </c>
       <c r="L84" s="104" t="n">
         <v>0.8082191781</v>
@@ -7714,7 +7714,7 @@
         <v/>
       </c>
       <c r="N84" s="104" t="n">
-        <v>0.0750439437519974</v>
+        <v>0.08231989555722589</v>
       </c>
       <c r="O84" s="104" t="n">
         <v>0.0611152139</v>
@@ -7788,10 +7788,10 @@
         </is>
       </c>
       <c r="C86" s="18" t="n">
-        <v>2</v>
+        <v>1.894736842105263</v>
       </c>
       <c r="D86" s="104" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.75</v>
       </c>
       <c r="E86" s="104" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v/>
       </c>
       <c r="N86" s="104" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.2545454545454545</v>
       </c>
       <c r="O86" s="104" t="n">
         <v>0.0611152139</v>
@@ -7847,13 +7847,13 @@
         </is>
       </c>
       <c r="C87" s="18" t="n">
-        <v>95.66666666666667</v>
+        <v>96.15789473684211</v>
       </c>
       <c r="D87" s="104" t="n">
-        <v>0.3700348432055749</v>
+        <v>0.378215654077723</v>
       </c>
       <c r="E87" s="104" t="n">
-        <v>0.832282</v>
+        <v>0.833014</v>
       </c>
       <c r="F87" s="104" t="n">
         <v>0.8087257009</v>
@@ -7863,7 +7863,7 @@
         <v/>
       </c>
       <c r="H87" s="104" t="n">
-        <v>0.780199</v>
+        <v>0.786158</v>
       </c>
       <c r="I87" s="104" t="n">
         <v>0.8207995184</v>
@@ -7873,7 +7873,7 @@
         <v/>
       </c>
       <c r="K87" s="104" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L87" s="104" t="n">
         <v>0.8082191781</v>
@@ -7883,7 +7883,7 @@
         <v/>
       </c>
       <c r="N87" s="104" t="n">
-        <v>0.0195141377937077</v>
+        <v>0.0173446862188584</v>
       </c>
       <c r="O87" s="104" t="n">
         <v>0.0611152139</v>
@@ -7973,7 +7973,7 @@
         <v>0</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E94" s="4" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
         <v>0</v>
       </c>
       <c r="D95" s="4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E95" s="4" t="n">
         <v>0</v>
@@ -10779,10 +10779,10 @@
         </is>
       </c>
       <c r="C149" s="116" t="n">
-        <v>0.2100804882819329</v>
+        <v>0.2083237677029555</v>
       </c>
       <c r="D149" s="116" t="n">
-        <v>0.335974</v>
+        <v>0.332953</v>
       </c>
       <c r="E149" s="20">
         <f>D149/C149</f>
@@ -10800,10 +10800,10 @@
         <v/>
       </c>
       <c r="I149" s="106" t="n">
-        <v>7788367.25</v>
+        <v>7796653.842105263</v>
       </c>
       <c r="J149" s="106" t="n">
-        <v>1487982.675145</v>
+        <v>1476822.691801</v>
       </c>
       <c r="K149" s="13" t="inlineStr">
         <is>
@@ -10818,10 +10818,10 @@
         </is>
       </c>
       <c r="C150" s="116" t="n">
-        <v>0.00677195226220127</v>
+        <v>0.00665428956107793</v>
       </c>
       <c r="D150" s="116" t="n">
-        <v>0.02880624824907791</v>
+        <v>0.02782999520629043</v>
       </c>
       <c r="E150" s="20">
         <f>D150/C150</f>
@@ -10839,10 +10839,10 @@
         <v/>
       </c>
       <c r="I150" s="106" t="n">
-        <v>5621606</v>
+        <v>6588703</v>
       </c>
       <c r="J150" s="106" t="n">
-        <v>2962708.56432</v>
+        <v>3385945.54841</v>
       </c>
     </row>
     <row r="152" ht="13.5" customHeight="1">

--- a/dist/downloads/精品货价监控指标_Sheet1.xlsx
+++ b/dist/downloads/精品货价监控指标_Sheet1.xlsx
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="C1" s="11" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="D1" s="11" t="inlineStr">
         <is>
@@ -1845,28 +1845,28 @@
         <v>71810000</v>
       </c>
       <c r="D6" s="103" t="n">
-        <v>41171977.66142999</v>
+        <v>43289792.78181999</v>
       </c>
       <c r="E6" s="104">
         <f>D6/C6</f>
         <v/>
       </c>
       <c r="F6" s="103" t="n">
-        <v>39870920.72767</v>
+        <v>42442675.40130001</v>
       </c>
       <c r="G6" s="104">
         <f>D6/F6-1</f>
         <v/>
       </c>
       <c r="H6" s="103" t="n">
-        <v>44282217.04154427</v>
+        <v>46425214.86260591</v>
       </c>
       <c r="I6" s="104">
         <f>D6/H6</f>
         <v/>
       </c>
       <c r="J6" s="103" t="n">
-        <v>44600000</v>
+        <v>46700000</v>
       </c>
       <c r="K6" s="104">
         <f>D6/J6</f>
@@ -1884,28 +1884,28 @@
         <v>132000000</v>
       </c>
       <c r="D7" s="103" t="n">
-        <v>58418083.24780001</v>
+        <v>61153197.11276</v>
       </c>
       <c r="E7" s="104">
         <f>D7/C7</f>
         <v/>
       </c>
       <c r="F7" s="103" t="n">
-        <v>65883708.92365</v>
+        <v>69851125.45231</v>
       </c>
       <c r="G7" s="104">
         <f>D7/F7-1</f>
         <v/>
       </c>
       <c r="H7" s="103" t="n">
-        <v>81398867.14223428</v>
+        <v>85338091.65664922</v>
       </c>
       <c r="I7" s="104">
         <f>D7/H7</f>
         <v/>
       </c>
       <c r="J7" s="103" t="n">
-        <v>82641342.7</v>
+        <v>87618566.3</v>
       </c>
       <c r="K7" s="104">
         <f>D7/J7</f>
@@ -1923,28 +1923,28 @@
         <v>9437018</v>
       </c>
       <c r="D8" s="103" t="n">
-        <v>7043379.949359999</v>
+        <v>7262340.18936</v>
       </c>
       <c r="E8" s="104">
         <f>D8/C8</f>
         <v/>
       </c>
       <c r="F8" s="103" t="n">
-        <v>4519848.26041</v>
+        <v>4870833.2415</v>
       </c>
       <c r="G8" s="104">
         <f>D8/F8-1</f>
         <v/>
       </c>
       <c r="H8" s="103" t="n">
-        <v>5819413.442430859</v>
+        <v>6101038.689768548</v>
       </c>
       <c r="I8" s="104">
         <f>D8/H8</f>
         <v/>
       </c>
       <c r="J8" s="103" t="n">
-        <v>5847018.15389968</v>
+        <v>6107018.15389968</v>
       </c>
       <c r="K8" s="104">
         <f>D8/J8</f>
@@ -1962,28 +1962,28 @@
         <v>88000000</v>
       </c>
       <c r="D9" s="103" t="n">
-        <v>50217161.58193</v>
+        <v>53139231.56896</v>
       </c>
       <c r="E9" s="104">
         <f>D9/C9</f>
         <v/>
       </c>
       <c r="F9" s="103" t="n">
-        <v>45786525.72287001</v>
+        <v>48081451.18179001</v>
       </c>
       <c r="G9" s="104">
         <f>D9/F9-1</f>
         <v/>
       </c>
       <c r="H9" s="103" t="n">
-        <v>54265911.42815619</v>
+        <v>56892061.10443281</v>
       </c>
       <c r="I9" s="104">
         <f>D9/H9</f>
         <v/>
       </c>
       <c r="J9" s="103" t="n">
-        <v>54575872</v>
+        <v>57308811</v>
       </c>
       <c r="K9" s="104">
         <f>D9/J9</f>
@@ -2001,28 +2001,28 @@
         <v>66000000</v>
       </c>
       <c r="D10" s="103" t="n">
-        <v>37166308.61001</v>
+        <v>38648926.94507</v>
       </c>
       <c r="E10" s="104">
         <f>D10/C10</f>
         <v/>
       </c>
       <c r="F10" s="103" t="n">
-        <v>35875548.66118</v>
+        <v>37426251.35981</v>
       </c>
       <c r="G10" s="104">
         <f>D10/F10-1</f>
         <v/>
       </c>
       <c r="H10" s="103" t="n">
-        <v>40699433.57111714</v>
+        <v>42669045.82832461</v>
       </c>
       <c r="I10" s="104">
         <f>D10/H10</f>
         <v/>
       </c>
       <c r="J10" s="103" t="n">
-        <v>41800000</v>
+        <v>43600000</v>
       </c>
       <c r="K10" s="104">
         <f>D10/J10</f>
@@ -2040,28 +2040,28 @@
         <v>62390797</v>
       </c>
       <c r="D11" s="103" t="n">
-        <v>29036981.66141</v>
+        <v>30363680.32967999</v>
       </c>
       <c r="E11" s="104">
         <f>D11/C11</f>
         <v/>
       </c>
       <c r="F11" s="103" t="n">
-        <v>32989934.38993</v>
+        <v>34599061.04399</v>
       </c>
       <c r="G11" s="104">
         <f>D11/F11-1</f>
         <v/>
       </c>
       <c r="H11" s="103" t="n">
-        <v>38473789.36288719</v>
+        <v>40335693.58270753</v>
       </c>
       <c r="I11" s="104">
         <f>D11/H11</f>
         <v/>
       </c>
       <c r="J11" s="103" t="n">
-        <v>40002249.98</v>
+        <v>41783216.00000001</v>
       </c>
       <c r="K11" s="104">
         <f>D11/J11</f>
@@ -10779,10 +10779,10 @@
         </is>
       </c>
       <c r="C149" s="116" t="n">
-        <v>0.2083237677029555</v>
+        <v>0.2069161860978783</v>
       </c>
       <c r="D149" s="116" t="n">
-        <v>0.332953</v>
+        <v>0.331403</v>
       </c>
       <c r="E149" s="20">
         <f>D149/C149</f>
@@ -10800,10 +10800,10 @@
         <v/>
       </c>
       <c r="I149" s="106" t="n">
-        <v>7796653.842105263</v>
+        <v>7726440.1</v>
       </c>
       <c r="J149" s="106" t="n">
-        <v>1476822.691801</v>
+        <v>1463587.648948</v>
       </c>
       <c r="K149" s="13" t="inlineStr">
         <is>

--- a/dist/downloads/精品货价监控指标_Sheet1.xlsx
+++ b/dist/downloads/精品货价监控指标_Sheet1.xlsx
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="C1" s="11" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="D1" s="11" t="inlineStr">
         <is>
@@ -1845,28 +1845,28 @@
         <v>71810000</v>
       </c>
       <c r="D6" s="103" t="n">
-        <v>43289792.78181999</v>
+        <v>45589046.04950999</v>
       </c>
       <c r="E6" s="104">
         <f>D6/C6</f>
         <v/>
       </c>
       <c r="F6" s="103" t="n">
-        <v>42442675.40130001</v>
+        <v>44748936.31879</v>
       </c>
       <c r="G6" s="104">
         <f>D6/F6-1</f>
         <v/>
       </c>
       <c r="H6" s="103" t="n">
-        <v>46425214.86260591</v>
+        <v>48732922.6058565</v>
       </c>
       <c r="I6" s="104">
         <f>D6/H6</f>
         <v/>
       </c>
       <c r="J6" s="103" t="n">
-        <v>46700000</v>
+        <v>48800000</v>
       </c>
       <c r="K6" s="104">
         <f>D6/J6</f>
@@ -1884,28 +1884,28 @@
         <v>132000000</v>
       </c>
       <c r="D7" s="103" t="n">
-        <v>61153197.11276</v>
+        <v>64286928.90509001</v>
       </c>
       <c r="E7" s="104">
         <f>D7/C7</f>
         <v/>
       </c>
       <c r="F7" s="103" t="n">
-        <v>69851125.45231</v>
+        <v>73099594.72197999</v>
       </c>
       <c r="G7" s="104">
         <f>D7/F7-1</f>
         <v/>
       </c>
       <c r="H7" s="103" t="n">
-        <v>85338091.65664922</v>
+        <v>89580083.33063722</v>
       </c>
       <c r="I7" s="104">
         <f>D7/H7</f>
         <v/>
       </c>
       <c r="J7" s="103" t="n">
-        <v>87618566.3</v>
+        <v>91691966.89999999</v>
       </c>
       <c r="K7" s="104">
         <f>D7/J7</f>
@@ -1923,28 +1923,28 @@
         <v>9437018</v>
       </c>
       <c r="D8" s="103" t="n">
-        <v>7262340.18936</v>
+        <v>7600357.68936</v>
       </c>
       <c r="E8" s="104">
         <f>D8/C8</f>
         <v/>
       </c>
       <c r="F8" s="103" t="n">
-        <v>4870833.2415</v>
+        <v>5177671.695250001</v>
       </c>
       <c r="G8" s="104">
         <f>D8/F8-1</f>
         <v/>
       </c>
       <c r="H8" s="103" t="n">
-        <v>6101038.689768548</v>
+        <v>6404309.53661154</v>
       </c>
       <c r="I8" s="104">
         <f>D8/H8</f>
         <v/>
       </c>
       <c r="J8" s="103" t="n">
-        <v>6107018.15389968</v>
+        <v>6457018.15389968</v>
       </c>
       <c r="K8" s="104">
         <f>D8/J8</f>
@@ -1962,28 +1962,28 @@
         <v>88000000</v>
       </c>
       <c r="D9" s="103" t="n">
-        <v>53139231.56896</v>
+        <v>55938957.81296</v>
       </c>
       <c r="E9" s="104">
         <f>D9/C9</f>
         <v/>
       </c>
       <c r="F9" s="103" t="n">
-        <v>48081451.18179001</v>
+        <v>50608246.44949001</v>
       </c>
       <c r="G9" s="104">
         <f>D9/F9-1</f>
         <v/>
       </c>
       <c r="H9" s="103" t="n">
-        <v>56892061.10443281</v>
+        <v>59720055.55375814</v>
       </c>
       <c r="I9" s="104">
         <f>D9/H9</f>
         <v/>
       </c>
       <c r="J9" s="103" t="n">
-        <v>57308811</v>
+        <v>60117581</v>
       </c>
       <c r="K9" s="104">
         <f>D9/J9</f>
@@ -2001,28 +2001,28 @@
         <v>66000000</v>
       </c>
       <c r="D10" s="103" t="n">
-        <v>38648926.94507</v>
+        <v>41020829.74684</v>
       </c>
       <c r="E10" s="104">
         <f>D10/C10</f>
         <v/>
       </c>
       <c r="F10" s="103" t="n">
-        <v>37426251.35981</v>
+        <v>39068688.49191999</v>
       </c>
       <c r="G10" s="104">
         <f>D10/F10-1</f>
         <v/>
       </c>
       <c r="H10" s="103" t="n">
-        <v>42669045.82832461</v>
+        <v>44790041.66531861</v>
       </c>
       <c r="I10" s="104">
         <f>D10/H10</f>
         <v/>
       </c>
       <c r="J10" s="103" t="n">
-        <v>43600000</v>
+        <v>45400000</v>
       </c>
       <c r="K10" s="104">
         <f>D10/J10</f>
@@ -2040,28 +2040,28 @@
         <v>62390797</v>
       </c>
       <c r="D11" s="103" t="n">
-        <v>30363680.32967999</v>
+        <v>31849970.08093</v>
       </c>
       <c r="E11" s="104">
         <f>D11/C11</f>
         <v/>
       </c>
       <c r="F11" s="103" t="n">
-        <v>34599061.04399</v>
+        <v>36672628.1319</v>
       </c>
       <c r="G11" s="104">
         <f>D11/F11-1</f>
         <v/>
       </c>
       <c r="H11" s="103" t="n">
-        <v>40335693.58270753</v>
+        <v>42340702.98730963</v>
       </c>
       <c r="I11" s="104">
         <f>D11/H11</f>
         <v/>
       </c>
       <c r="J11" s="103" t="n">
-        <v>41783216.00000001</v>
+        <v>43728188.65000001</v>
       </c>
       <c r="K11" s="104">
         <f>D11/J11</f>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="C46" s="107" t="n">
-        <v>116.46168</v>
+        <v>116.50236</v>
       </c>
       <c r="D46" s="108" t="n">
         <v>120</v>
@@ -3952,31 +3952,31 @@
         <v>0</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>0.970514</v>
+        <v>0.970853</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>0.029486</v>
+        <v>0.029147</v>
       </c>
       <c r="H46" s="104" t="n">
-        <v>0.792861</v>
+        <v>0.790543</v>
       </c>
       <c r="I46" s="104" t="n">
-        <v>0.823144</v>
+        <v>0.825946</v>
       </c>
       <c r="J46" s="14" t="n">
-        <v>-3.0283</v>
+        <v>-3.5403</v>
       </c>
       <c r="K46" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L46" s="104" t="n">
-        <v>0.980118</v>
+        <v>0.981071</v>
       </c>
       <c r="M46" s="104" t="n">
-        <v>0.853844</v>
+        <v>0.8566459999999999</v>
       </c>
       <c r="N46" s="14" t="n">
-        <v>12.62739999999999</v>
+        <v>12.44250000000001</v>
       </c>
       <c r="O46" s="14" t="n">
         <v>-2</v>
@@ -3999,31 +3999,31 @@
         <v>0</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>0.547494</v>
+        <v>0.559321</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>0.452506</v>
+        <v>0.440679</v>
       </c>
       <c r="H47" s="104" t="n">
-        <v>0.851843</v>
+        <v>0.856669</v>
       </c>
       <c r="I47" s="104" t="n">
-        <v>0.849729</v>
+        <v>0.8493889999999999</v>
       </c>
       <c r="J47" s="14" t="n">
-        <v>0.2114</v>
+        <v>0.728</v>
       </c>
       <c r="K47" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L47" s="104" t="n">
-        <v>0.951146</v>
+        <v>0.949338</v>
       </c>
       <c r="M47" s="104" t="n">
-        <v>0.8804289999999999</v>
+        <v>0.880089</v>
       </c>
       <c r="N47" s="14" t="n">
-        <v>7.071700000000007</v>
+        <v>6.924900000000008</v>
       </c>
       <c r="O47" s="14" t="n">
         <v>-2</v>
@@ -4037,40 +4037,40 @@
         </is>
       </c>
       <c r="C48" s="107" t="n">
-        <v>97.47265964</v>
+        <v>109.828543758</v>
       </c>
       <c r="D48" s="108" t="n">
-        <v>95.402</v>
+        <v>108.906</v>
       </c>
       <c r="E48" s="108" t="n">
         <v>120</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>0.91582</v>
+        <v>0.916843</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>0.08418</v>
+        <v>0.08315699999999999</v>
       </c>
       <c r="H48" s="104" t="n">
-        <v>0.757598</v>
+        <v>0.753799</v>
       </c>
       <c r="I48" s="104" t="n">
-        <v>0.775299</v>
+        <v>0.7782520000000001</v>
       </c>
       <c r="J48" s="14" t="n">
-        <v>-1.7701</v>
+        <v>-2.4453</v>
       </c>
       <c r="K48" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L48" s="104" t="n">
-        <v>0.74193</v>
+        <v>0.736854</v>
       </c>
       <c r="M48" s="104" t="n">
-        <v>0.8059989999999999</v>
+        <v>0.8089519999999999</v>
       </c>
       <c r="N48" s="14" t="n">
-        <v>-6.406899999999993</v>
+        <v>-7.209799999999987</v>
       </c>
       <c r="O48" s="14" t="n">
         <v>-2</v>
@@ -4084,40 +4084,40 @@
         </is>
       </c>
       <c r="C49" s="107" t="n">
-        <v>89.49326068799999</v>
+        <v>90.611526224</v>
       </c>
       <c r="D49" s="108" t="n">
-        <v>102.616</v>
+        <v>103.828</v>
       </c>
       <c r="E49" s="108" t="n">
         <v>0</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>0.8721179999999999</v>
+        <v>0.872708</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>0.127882</v>
+        <v>0.127292</v>
       </c>
       <c r="H49" s="104" t="n">
-        <v>0.80793</v>
+        <v>0.807859</v>
       </c>
       <c r="I49" s="104" t="n">
-        <v>0.829238</v>
+        <v>0.829773</v>
       </c>
       <c r="J49" s="14" t="n">
-        <v>-2.1308</v>
+        <v>-2.1914</v>
       </c>
       <c r="K49" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L49" s="104" t="n">
-        <v>0.87088</v>
+        <v>0.870929</v>
       </c>
       <c r="M49" s="104" t="n">
-        <v>0.859938</v>
+        <v>0.8604729999999999</v>
       </c>
       <c r="N49" s="14" t="n">
-        <v>1.094200000000001</v>
+        <v>1.045600000000007</v>
       </c>
       <c r="O49" s="14" t="n">
         <v>-2</v>
@@ -4140,31 +4140,31 @@
         <v>0</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>0.820179</v>
+        <v>0.819945</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>0.179821</v>
+        <v>0.180055</v>
       </c>
       <c r="H50" s="104" t="n">
-        <v>0.886393</v>
+        <v>0.887614</v>
       </c>
       <c r="I50" s="104" t="n">
-        <v>0.835625</v>
+        <v>0.8361189999999999</v>
       </c>
       <c r="J50" s="14" t="n">
-        <v>5.0768</v>
+        <v>5.1495</v>
       </c>
       <c r="K50" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L50" s="104" t="n">
-        <v>0.887994</v>
+        <v>0.8876309999999999</v>
       </c>
       <c r="M50" s="104" t="n">
-        <v>0.8663249999999999</v>
+        <v>0.866819</v>
       </c>
       <c r="N50" s="14" t="n">
-        <v>2.166900000000012</v>
+        <v>2.081199999999995</v>
       </c>
       <c r="O50" s="14" t="n">
         <v>-2</v>
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="C69" s="10" t="n">
-        <v>0.9391932047017469</v>
+        <v>0.9377664531082669</v>
       </c>
       <c r="D69" s="10" t="n">
-        <v>0.9300424722153577</v>
+        <v>0.9295606008002918</v>
       </c>
       <c r="E69" s="10">
         <f>D69-C69</f>
@@ -6886,10 +6886,10 @@
         </is>
       </c>
       <c r="C70" s="10" t="n">
-        <v>0.9342072505209006</v>
+        <v>0.9331097747525502</v>
       </c>
       <c r="D70" s="10" t="n">
-        <v>0.8890427547929984</v>
+        <v>0.889161285998024</v>
       </c>
       <c r="E70" s="10">
         <f>D70-C70</f>
@@ -6975,10 +6975,10 @@
         </is>
       </c>
       <c r="C71" s="10" t="n">
-        <v>0.9281154743709659</v>
+        <v>0.9262097744348601</v>
       </c>
       <c r="D71" s="10" t="n">
-        <v>0.8884953019252709</v>
+        <v>0.8903262920570877</v>
       </c>
       <c r="E71" s="10">
         <f>D71-C71</f>
@@ -7064,10 +7064,10 @@
         </is>
       </c>
       <c r="C72" s="10" t="n">
-        <v>0.974922644430219</v>
+        <v>0.9759493574653033</v>
       </c>
       <c r="D72" s="10" t="n">
-        <v>0.8723162364702726</v>
+        <v>0.874971963372827</v>
       </c>
       <c r="E72" s="10">
         <f>D72-C72</f>
@@ -7153,10 +7153,10 @@
         </is>
       </c>
       <c r="C73" s="10" t="n">
-        <v>0.9457953338027764</v>
+        <v>0.944278190056519</v>
       </c>
       <c r="D73" s="10" t="n">
-        <v>0.8367295224048984</v>
+        <v>0.8335662778560988</v>
       </c>
       <c r="E73" s="10">
         <f>D73-C73</f>
@@ -7242,10 +7242,10 @@
         </is>
       </c>
       <c r="C74" s="10" t="n">
-        <v>0.9421029888053504</v>
+        <v>0.9420106884871495</v>
       </c>
       <c r="D74" s="10" t="n">
-        <v>0.879677870232397</v>
+        <v>0.8797788230581509</v>
       </c>
       <c r="E74" s="10">
         <f>D74-C74</f>
@@ -7331,10 +7331,10 @@
         </is>
       </c>
       <c r="C75" s="10" t="n">
-        <v>0.9380595280669098</v>
+        <v>0.9372072413951775</v>
       </c>
       <c r="D75" s="10" t="n">
-        <v>0.884070603110812</v>
+        <v>0.884462242152963</v>
       </c>
       <c r="E75" s="10">
         <f>D75-C75</f>
@@ -7517,13 +7517,13 @@
         </is>
       </c>
       <c r="C81" s="18" t="n">
-        <v>1417.578947368421</v>
+        <v>1415.35</v>
       </c>
       <c r="D81" s="104" t="n">
-        <v>0.7105145912229895</v>
+        <v>0.7109195605327304</v>
       </c>
       <c r="E81" s="104" t="n">
-        <v>0.89395</v>
+        <v>0.894324</v>
       </c>
       <c r="F81" s="104" t="n">
         <v>0.8146325152</v>
@@ -7533,7 +7533,7 @@
         <v/>
       </c>
       <c r="H81" s="104" t="n">
-        <v>0.8848</v>
+        <v>0.885115</v>
       </c>
       <c r="I81" s="104" t="n">
         <v>0.8207995184</v>
@@ -7543,7 +7543,7 @@
         <v/>
       </c>
       <c r="K81" s="104" t="n">
-        <v>0.8059210526315789</v>
+        <v>0.8081761006289307</v>
       </c>
       <c r="L81" s="104" t="n">
         <v>0.8082191781</v>
@@ -7553,7 +7553,7 @@
         <v/>
       </c>
       <c r="N81" s="104" t="n">
-        <v>0.0712106478980485</v>
+        <v>0.0719065675122228</v>
       </c>
       <c r="O81" s="104" t="n">
         <v>0.0611152139</v>
@@ -7570,13 +7570,13 @@
         </is>
       </c>
       <c r="C82" s="18" t="n">
-        <v>115.4736842105263</v>
+        <v>115.85</v>
       </c>
       <c r="D82" s="104" t="n">
-        <v>0.2525068368277119</v>
+        <v>0.2537764350453172</v>
       </c>
       <c r="E82" s="104" t="n">
-        <v>0.729419</v>
+        <v>0.730587</v>
       </c>
       <c r="F82" s="104" t="n">
         <v>0.7556221149</v>
@@ -7608,7 +7608,7 @@
         <v/>
       </c>
       <c r="N82" s="104" t="n">
-        <v>0.1462979482604817</v>
+        <v>0.1457627118644068</v>
       </c>
       <c r="O82" s="104" t="n">
         <v>0.0611152139</v>
@@ -7625,13 +7625,13 @@
         </is>
       </c>
       <c r="C83" s="18" t="n">
-        <v>323.9473684210527</v>
+        <v>322.25</v>
       </c>
       <c r="D83" s="104" t="n">
-        <v>0.7166531275385865</v>
+        <v>0.7154383242823894</v>
       </c>
       <c r="E83" s="104" t="n">
-        <v>0.884624</v>
+        <v>0.884232</v>
       </c>
       <c r="F83" s="104" t="n">
         <v>0.8066</v>
@@ -7641,7 +7641,7 @@
         <v/>
       </c>
       <c r="H83" s="104" t="n">
-        <v>0.8840479999999999</v>
+        <v>0.8841869999999999</v>
       </c>
       <c r="I83" s="104" t="n">
         <v>0.8207995184</v>
@@ -7651,7 +7651,7 @@
         <v/>
       </c>
       <c r="K83" s="104" t="n">
-        <v>0.9375</v>
+        <v>0.9464285714285714</v>
       </c>
       <c r="L83" s="104" t="n">
         <v>0.8082191781</v>
@@ -7661,7 +7661,7 @@
         <v/>
       </c>
       <c r="N83" s="104" t="n">
-        <v>0.0537193203272498</v>
+        <v>0.0524923654026499</v>
       </c>
       <c r="O83" s="104" t="n">
         <v>0.0611152139</v>
@@ -7678,13 +7678,13 @@
         </is>
       </c>
       <c r="C84" s="18" t="n">
-        <v>879.578947368421</v>
+        <v>878.6</v>
       </c>
       <c r="D84" s="104" t="n">
-        <v>0.804571565342269</v>
+        <v>0.8057136353289324</v>
       </c>
       <c r="E84" s="104" t="n">
-        <v>0.912312</v>
+        <v>0.913868</v>
       </c>
       <c r="F84" s="104" t="n">
         <v>0.8078</v>
@@ -7694,7 +7694,7 @@
         <v/>
       </c>
       <c r="H84" s="104" t="n">
-        <v>0.890002</v>
+        <v>0.891497</v>
       </c>
       <c r="I84" s="104" t="n">
         <v>0.8207995184</v>
@@ -7704,7 +7704,7 @@
         <v/>
       </c>
       <c r="K84" s="104" t="n">
-        <v>0.7831325301204819</v>
+        <v>0.7808764940239044</v>
       </c>
       <c r="L84" s="104" t="n">
         <v>0.8082191781</v>
@@ -7714,7 +7714,7 @@
         <v/>
       </c>
       <c r="N84" s="104" t="n">
-        <v>0.08231989555722589</v>
+        <v>0.0839250886691717</v>
       </c>
       <c r="O84" s="104" t="n">
         <v>0.0611152139</v>
@@ -7788,10 +7788,10 @@
         </is>
       </c>
       <c r="C86" s="18" t="n">
-        <v>1.894736842105263</v>
+        <v>1.85</v>
       </c>
       <c r="D86" s="104" t="n">
-        <v>0.75</v>
+        <v>0.7567567567567568</v>
       </c>
       <c r="E86" s="104" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v/>
       </c>
       <c r="N86" s="104" t="n">
-        <v>0.2545454545454545</v>
+        <v>0.2456140350877193</v>
       </c>
       <c r="O86" s="104" t="n">
         <v>0.0611152139</v>
@@ -7847,13 +7847,13 @@
         </is>
       </c>
       <c r="C87" s="18" t="n">
-        <v>96.15789473684211</v>
+        <v>96.3</v>
       </c>
       <c r="D87" s="104" t="n">
-        <v>0.378215654077723</v>
+        <v>0.3795430944963655</v>
       </c>
       <c r="E87" s="104" t="n">
-        <v>0.833014</v>
+        <v>0.834858</v>
       </c>
       <c r="F87" s="104" t="n">
         <v>0.8087257009</v>
@@ -7863,7 +7863,7 @@
         <v/>
       </c>
       <c r="H87" s="104" t="n">
-        <v>0.786158</v>
+        <v>0.787304</v>
       </c>
       <c r="I87" s="104" t="n">
         <v>0.8207995184</v>
@@ -7873,7 +7873,7 @@
         <v/>
       </c>
       <c r="K87" s="104" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="L87" s="104" t="n">
         <v>0.8082191781</v>
@@ -7883,7 +7883,7 @@
         <v/>
       </c>
       <c r="N87" s="104" t="n">
-        <v>0.0173446862188584</v>
+        <v>0.0167714884696017</v>
       </c>
       <c r="O87" s="104" t="n">
         <v>0.0611152139</v>
@@ -10779,10 +10779,10 @@
         </is>
       </c>
       <c r="C149" s="116" t="n">
-        <v>0.2069161860978783</v>
+        <v>0.2064424084151716</v>
       </c>
       <c r="D149" s="116" t="n">
-        <v>0.331403</v>
+        <v>0.332475</v>
       </c>
       <c r="E149" s="20">
         <f>D149/C149</f>
@@ -10800,10 +10800,10 @@
         <v/>
       </c>
       <c r="I149" s="106" t="n">
-        <v>7726440.1</v>
+        <v>7707249.476190476</v>
       </c>
       <c r="J149" s="106" t="n">
-        <v>1463587.648948</v>
+        <v>1467249.25156</v>
       </c>
       <c r="K149" s="13" t="inlineStr">
         <is>
@@ -10818,10 +10818,10 @@
         </is>
       </c>
       <c r="C150" s="116" t="n">
-        <v>0.00665428956107793</v>
+        <v>0.00673394578260548</v>
       </c>
       <c r="D150" s="116" t="n">
-        <v>0.02782999520629043</v>
+        <v>0.02802774511698452</v>
       </c>
       <c r="E150" s="20">
         <f>D150/C150</f>
@@ -10839,10 +10839,10 @@
         <v/>
       </c>
       <c r="I150" s="106" t="n">
-        <v>6588703</v>
+        <v>7351980</v>
       </c>
       <c r="J150" s="106" t="n">
-        <v>3385945.54841</v>
+        <v>3749215.65042</v>
       </c>
     </row>
     <row r="152" ht="13.5" customHeight="1">

--- a/dist/downloads/精品货价监控指标_Sheet1.xlsx
+++ b/dist/downloads/精品货价监控指标_Sheet1.xlsx
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="C1" s="11" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="D1" s="11" t="inlineStr">
         <is>
@@ -1845,28 +1845,28 @@
         <v>71810000</v>
       </c>
       <c r="D6" s="103" t="n">
-        <v>45589046.04950999</v>
+        <v>47525575.17379998</v>
       </c>
       <c r="E6" s="104">
         <f>D6/C6</f>
         <v/>
       </c>
       <c r="F6" s="103" t="n">
-        <v>44748936.31879</v>
+        <v>46784690.49070001</v>
       </c>
       <c r="G6" s="104">
         <f>D6/F6-1</f>
         <v/>
       </c>
       <c r="H6" s="103" t="n">
-        <v>48732922.6058565</v>
+        <v>51040630.3491071</v>
       </c>
       <c r="I6" s="104">
         <f>D6/H6</f>
         <v/>
       </c>
       <c r="J6" s="103" t="n">
-        <v>48800000</v>
+        <v>50900000</v>
       </c>
       <c r="K6" s="104">
         <f>D6/J6</f>
@@ -1884,28 +1884,28 @@
         <v>132000000</v>
       </c>
       <c r="D7" s="103" t="n">
-        <v>64286928.90509001</v>
+        <v>67149527.50237</v>
       </c>
       <c r="E7" s="104">
         <f>D7/C7</f>
         <v/>
       </c>
       <c r="F7" s="103" t="n">
-        <v>73099594.72197999</v>
+        <v>76362319.94632</v>
       </c>
       <c r="G7" s="104">
         <f>D7/F7-1</f>
         <v/>
       </c>
       <c r="H7" s="103" t="n">
-        <v>89580083.33063722</v>
+        <v>93822075.00462522</v>
       </c>
       <c r="I7" s="104">
         <f>D7/H7</f>
         <v/>
       </c>
       <c r="J7" s="103" t="n">
-        <v>91691966.89999999</v>
+        <v>95784903.69999999</v>
       </c>
       <c r="K7" s="104">
         <f>D7/J7</f>
@@ -1923,28 +1923,28 @@
         <v>9437018</v>
       </c>
       <c r="D8" s="103" t="n">
-        <v>7600357.68936</v>
+        <v>7852956.128949999</v>
       </c>
       <c r="E8" s="104">
         <f>D8/C8</f>
         <v/>
       </c>
       <c r="F8" s="103" t="n">
-        <v>5177671.695250001</v>
+        <v>5373553.104139999</v>
       </c>
       <c r="G8" s="104">
         <f>D8/F8-1</f>
         <v/>
       </c>
       <c r="H8" s="103" t="n">
-        <v>6404309.53661154</v>
+        <v>6707580.383454532</v>
       </c>
       <c r="I8" s="104">
         <f>D8/H8</f>
         <v/>
       </c>
       <c r="J8" s="103" t="n">
-        <v>6457018.15389968</v>
+        <v>6717018.15389968</v>
       </c>
       <c r="K8" s="104">
         <f>D8/J8</f>
@@ -1962,28 +1962,28 @@
         <v>88000000</v>
       </c>
       <c r="D9" s="103" t="n">
-        <v>55938957.81296</v>
+        <v>59910928.16398</v>
       </c>
       <c r="E9" s="104">
         <f>D9/C9</f>
         <v/>
       </c>
       <c r="F9" s="103" t="n">
-        <v>50608246.44949001</v>
+        <v>52905814.67994001</v>
       </c>
       <c r="G9" s="104">
         <f>D9/F9-1</f>
         <v/>
       </c>
       <c r="H9" s="103" t="n">
-        <v>59720055.55375814</v>
+        <v>62548050.00308348</v>
       </c>
       <c r="I9" s="104">
         <f>D9/H9</f>
         <v/>
       </c>
       <c r="J9" s="103" t="n">
-        <v>60117581</v>
+        <v>64104255</v>
       </c>
       <c r="K9" s="104">
         <f>D9/J9</f>
@@ -2001,28 +2001,28 @@
         <v>66000000</v>
       </c>
       <c r="D10" s="103" t="n">
-        <v>41020829.74684</v>
+        <v>42452329.48069</v>
       </c>
       <c r="E10" s="104">
         <f>D10/C10</f>
         <v/>
       </c>
       <c r="F10" s="103" t="n">
-        <v>39068688.49191999</v>
+        <v>40679482.70381999</v>
       </c>
       <c r="G10" s="104">
         <f>D10/F10-1</f>
         <v/>
       </c>
       <c r="H10" s="103" t="n">
-        <v>44790041.66531861</v>
+        <v>46911037.50231261</v>
       </c>
       <c r="I10" s="104">
         <f>D10/H10</f>
         <v/>
       </c>
       <c r="J10" s="103" t="n">
-        <v>45400000</v>
+        <v>47200000</v>
       </c>
       <c r="K10" s="104">
         <f>D10/J10</f>
@@ -2040,28 +2040,28 @@
         <v>62390797</v>
       </c>
       <c r="D11" s="103" t="n">
-        <v>31849970.08093</v>
+        <v>33202502.2384</v>
       </c>
       <c r="E11" s="104">
         <f>D11/C11</f>
         <v/>
       </c>
       <c r="F11" s="103" t="n">
-        <v>36672628.1319</v>
+        <v>38581436.85924</v>
       </c>
       <c r="G11" s="104">
         <f>D11/F11-1</f>
         <v/>
       </c>
       <c r="H11" s="103" t="n">
-        <v>42340702.98730963</v>
+        <v>44345712.39191172</v>
       </c>
       <c r="I11" s="104">
         <f>D11/H11</f>
         <v/>
       </c>
       <c r="J11" s="103" t="n">
-        <v>43728188.65000001</v>
+        <v>45509154.67000001</v>
       </c>
       <c r="K11" s="104">
         <f>D11/J11</f>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="C46" s="107" t="n">
-        <v>116.50236</v>
+        <v>116.47248</v>
       </c>
       <c r="D46" s="108" t="n">
         <v>120</v>
@@ -3952,31 +3952,31 @@
         <v>0</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>0.970853</v>
+        <v>0.970604</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>0.029147</v>
+        <v>0.029396</v>
       </c>
       <c r="H46" s="104" t="n">
-        <v>0.790543</v>
+        <v>0.790282</v>
       </c>
       <c r="I46" s="104" t="n">
-        <v>0.825946</v>
+        <v>0.83053</v>
       </c>
       <c r="J46" s="14" t="n">
-        <v>-3.5403</v>
+        <v>-4.0248</v>
       </c>
       <c r="K46" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L46" s="104" t="n">
-        <v>0.981071</v>
+        <v>0.981855</v>
       </c>
       <c r="M46" s="104" t="n">
-        <v>0.8566459999999999</v>
+        <v>0.8612299999999999</v>
       </c>
       <c r="N46" s="14" t="n">
-        <v>12.44250000000001</v>
+        <v>12.06250000000001</v>
       </c>
       <c r="O46" s="14" t="n">
         <v>-2</v>
@@ -3999,31 +3999,31 @@
         <v>0</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>0.559321</v>
+        <v>0.548767</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>0.440679</v>
+        <v>0.451233</v>
       </c>
       <c r="H47" s="104" t="n">
-        <v>0.856669</v>
+        <v>0.857147</v>
       </c>
       <c r="I47" s="104" t="n">
-        <v>0.8493889999999999</v>
+        <v>0.8485</v>
       </c>
       <c r="J47" s="14" t="n">
-        <v>0.728</v>
+        <v>0.8647</v>
       </c>
       <c r="K47" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L47" s="104" t="n">
-        <v>0.949338</v>
+        <v>0.950507</v>
       </c>
       <c r="M47" s="104" t="n">
-        <v>0.880089</v>
+        <v>0.8791999999999999</v>
       </c>
       <c r="N47" s="14" t="n">
-        <v>6.924900000000008</v>
+        <v>7.130700000000019</v>
       </c>
       <c r="O47" s="14" t="n">
         <v>-2</v>
@@ -4037,40 +4037,40 @@
         </is>
       </c>
       <c r="C48" s="107" t="n">
-        <v>109.828543758</v>
+        <v>110.34237613</v>
       </c>
       <c r="D48" s="108" t="n">
-        <v>108.906</v>
+        <v>109.466</v>
       </c>
       <c r="E48" s="108" t="n">
         <v>120</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>0.916843</v>
+        <v>0.916805</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>0.08315699999999999</v>
+        <v>0.08319500000000001</v>
       </c>
       <c r="H48" s="104" t="n">
-        <v>0.753799</v>
+        <v>0.753354</v>
       </c>
       <c r="I48" s="104" t="n">
-        <v>0.7782520000000001</v>
+        <v>0.778087</v>
       </c>
       <c r="J48" s="14" t="n">
-        <v>-2.4453</v>
+        <v>-2.4733</v>
       </c>
       <c r="K48" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L48" s="104" t="n">
-        <v>0.736854</v>
+        <v>0.736253</v>
       </c>
       <c r="M48" s="104" t="n">
-        <v>0.8089519999999999</v>
+        <v>0.8087869999999999</v>
       </c>
       <c r="N48" s="14" t="n">
-        <v>-7.209799999999987</v>
+        <v>-7.253399999999999</v>
       </c>
       <c r="O48" s="14" t="n">
         <v>-2</v>
@@ -4084,40 +4084,40 @@
         </is>
       </c>
       <c r="C49" s="107" t="n">
-        <v>90.611526224</v>
+        <v>89.945364064</v>
       </c>
       <c r="D49" s="108" t="n">
-        <v>103.828</v>
+        <v>102.944</v>
       </c>
       <c r="E49" s="108" t="n">
         <v>0</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>0.872708</v>
+        <v>0.873731</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>0.127292</v>
+        <v>0.126269</v>
       </c>
       <c r="H49" s="104" t="n">
-        <v>0.807859</v>
+        <v>0.808609</v>
       </c>
       <c r="I49" s="104" t="n">
-        <v>0.829773</v>
+        <v>0.830081</v>
       </c>
       <c r="J49" s="14" t="n">
-        <v>-2.1914</v>
+        <v>-2.1472</v>
       </c>
       <c r="K49" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L49" s="104" t="n">
-        <v>0.870929</v>
+        <v>0.870567</v>
       </c>
       <c r="M49" s="104" t="n">
-        <v>0.8604729999999999</v>
+        <v>0.8607809999999999</v>
       </c>
       <c r="N49" s="14" t="n">
-        <v>1.045600000000007</v>
+        <v>0.9786000000000143</v>
       </c>
       <c r="O49" s="14" t="n">
         <v>-2</v>
@@ -4140,31 +4140,31 @@
         <v>0</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>0.819945</v>
+        <v>0.819897</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>0.180055</v>
+        <v>0.180103</v>
       </c>
       <c r="H50" s="104" t="n">
-        <v>0.887614</v>
+        <v>0.8876540000000001</v>
       </c>
       <c r="I50" s="104" t="n">
-        <v>0.8361189999999999</v>
+        <v>0.8362540000000001</v>
       </c>
       <c r="J50" s="14" t="n">
-        <v>5.1495</v>
+        <v>5.14</v>
       </c>
       <c r="K50" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L50" s="104" t="n">
-        <v>0.8876309999999999</v>
+        <v>0.886872</v>
       </c>
       <c r="M50" s="104" t="n">
-        <v>0.866819</v>
+        <v>0.8669539999999999</v>
       </c>
       <c r="N50" s="14" t="n">
-        <v>2.081199999999995</v>
+        <v>1.991800000000012</v>
       </c>
       <c r="O50" s="14" t="n">
         <v>-2</v>
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="C69" s="10" t="n">
-        <v>0.9377664531082669</v>
+        <v>0.9383307347157092</v>
       </c>
       <c r="D69" s="10" t="n">
-        <v>0.9295606008002918</v>
+        <v>0.92959908861528</v>
       </c>
       <c r="E69" s="10">
         <f>D69-C69</f>
@@ -6886,10 +6886,10 @@
         </is>
       </c>
       <c r="C70" s="10" t="n">
-        <v>0.9331097747525502</v>
+        <v>0.9324869092347707</v>
       </c>
       <c r="D70" s="10" t="n">
-        <v>0.889161285998024</v>
+        <v>0.8893768496515304</v>
       </c>
       <c r="E70" s="10">
         <f>D70-C70</f>
@@ -6975,10 +6975,10 @@
         </is>
       </c>
       <c r="C71" s="10" t="n">
-        <v>0.9262097744348601</v>
+        <v>0.925484107726843</v>
       </c>
       <c r="D71" s="10" t="n">
-        <v>0.8903262920570877</v>
+        <v>0.8903021331892945</v>
       </c>
       <c r="E71" s="10">
         <f>D71-C71</f>
@@ -7064,10 +7064,10 @@
         </is>
       </c>
       <c r="C72" s="10" t="n">
-        <v>0.9759493574653033</v>
+        <v>0.976732113881141</v>
       </c>
       <c r="D72" s="10" t="n">
-        <v>0.874971963372827</v>
+        <v>0.8759961244614934</v>
       </c>
       <c r="E72" s="10">
         <f>D72-C72</f>
@@ -7153,10 +7153,10 @@
         </is>
       </c>
       <c r="C73" s="10" t="n">
-        <v>0.944278190056519</v>
+        <v>0.9436485456006595</v>
       </c>
       <c r="D73" s="10" t="n">
-        <v>0.8335662778560988</v>
+        <v>0.832181997564462</v>
       </c>
       <c r="E73" s="10">
         <f>D73-C73</f>
@@ -7242,10 +7242,10 @@
         </is>
       </c>
       <c r="C74" s="10" t="n">
-        <v>0.9420106884871495</v>
+        <v>0.9408606658083472</v>
       </c>
       <c r="D74" s="10" t="n">
-        <v>0.8797788230581509</v>
+        <v>0.879219019959161</v>
       </c>
       <c r="E74" s="10">
         <f>D74-C74</f>
@@ -7331,10 +7331,10 @@
         </is>
       </c>
       <c r="C75" s="10" t="n">
-        <v>0.9372072413951775</v>
+        <v>0.9365345017520862</v>
       </c>
       <c r="D75" s="10" t="n">
-        <v>0.884462242152963</v>
+        <v>0.8844618193862247</v>
       </c>
       <c r="E75" s="10">
         <f>D75-C75</f>
@@ -7517,13 +7517,13 @@
         </is>
       </c>
       <c r="C81" s="18" t="n">
-        <v>1415.35</v>
+        <v>1412.272727272727</v>
       </c>
       <c r="D81" s="104" t="n">
-        <v>0.7109195605327304</v>
+        <v>0.7101383971676859</v>
       </c>
       <c r="E81" s="104" t="n">
-        <v>0.894324</v>
+        <v>0.894188</v>
       </c>
       <c r="F81" s="104" t="n">
         <v>0.8146325152</v>
@@ -7533,7 +7533,7 @@
         <v/>
       </c>
       <c r="H81" s="104" t="n">
-        <v>0.885115</v>
+        <v>0.885545</v>
       </c>
       <c r="I81" s="104" t="n">
         <v>0.8207995184</v>
@@ -7543,7 +7543,7 @@
         <v/>
       </c>
       <c r="K81" s="104" t="n">
-        <v>0.8081761006289307</v>
+        <v>0.8211143695014663</v>
       </c>
       <c r="L81" s="104" t="n">
         <v>0.8082191781</v>
@@ -7553,7 +7553,7 @@
         <v/>
       </c>
       <c r="N81" s="104" t="n">
-        <v>0.0719065675122228</v>
+        <v>0.073307413862448</v>
       </c>
       <c r="O81" s="104" t="n">
         <v>0.0611152139</v>
@@ -7570,13 +7570,13 @@
         </is>
       </c>
       <c r="C82" s="18" t="n">
-        <v>115.85</v>
+        <v>116.5909090909091</v>
       </c>
       <c r="D82" s="104" t="n">
-        <v>0.2537764350453172</v>
+        <v>0.2514619883040936</v>
       </c>
       <c r="E82" s="104" t="n">
-        <v>0.730587</v>
+        <v>0.729693</v>
       </c>
       <c r="F82" s="104" t="n">
         <v>0.7556221149</v>
@@ -7608,7 +7608,7 @@
         <v/>
       </c>
       <c r="N82" s="104" t="n">
-        <v>0.1457627118644068</v>
+        <v>0.1486902927580894</v>
       </c>
       <c r="O82" s="104" t="n">
         <v>0.0611152139</v>
@@ -7625,13 +7625,13 @@
         </is>
       </c>
       <c r="C83" s="18" t="n">
-        <v>322.25</v>
+        <v>319.3181818181818</v>
       </c>
       <c r="D83" s="104" t="n">
-        <v>0.7154383242823894</v>
+        <v>0.7117437722419929</v>
       </c>
       <c r="E83" s="104" t="n">
-        <v>0.884232</v>
+        <v>0.883387</v>
       </c>
       <c r="F83" s="104" t="n">
         <v>0.8066</v>
@@ -7641,7 +7641,7 @@
         <v/>
       </c>
       <c r="H83" s="104" t="n">
-        <v>0.8841869999999999</v>
+        <v>0.8843569999999999</v>
       </c>
       <c r="I83" s="104" t="n">
         <v>0.8207995184</v>
@@ -7651,7 +7651,7 @@
         <v/>
       </c>
       <c r="K83" s="104" t="n">
-        <v>0.9464285714285714</v>
+        <v>0.9491525423728814</v>
       </c>
       <c r="L83" s="104" t="n">
         <v>0.8082191781</v>
@@ -7661,7 +7661,7 @@
         <v/>
       </c>
       <c r="N83" s="104" t="n">
-        <v>0.0524923654026499</v>
+        <v>0.0509589282955574</v>
       </c>
       <c r="O83" s="104" t="n">
         <v>0.0611152139</v>
@@ -7678,13 +7678,13 @@
         </is>
       </c>
       <c r="C84" s="18" t="n">
-        <v>878.6</v>
+        <v>877.5909090909091</v>
       </c>
       <c r="D84" s="104" t="n">
-        <v>0.8057136353289324</v>
+        <v>0.8066504376650956</v>
       </c>
       <c r="E84" s="104" t="n">
-        <v>0.913868</v>
+        <v>0.914772</v>
       </c>
       <c r="F84" s="104" t="n">
         <v>0.8078</v>
@@ -7694,7 +7694,7 @@
         <v/>
       </c>
       <c r="H84" s="104" t="n">
-        <v>0.891497</v>
+        <v>0.89377</v>
       </c>
       <c r="I84" s="104" t="n">
         <v>0.8207995184</v>
@@ -7704,7 +7704,7 @@
         <v/>
       </c>
       <c r="K84" s="104" t="n">
-        <v>0.7808764940239044</v>
+        <v>0.7970479704797048</v>
       </c>
       <c r="L84" s="104" t="n">
         <v>0.8082191781</v>
@@ -7714,7 +7714,7 @@
         <v/>
       </c>
       <c r="N84" s="104" t="n">
-        <v>0.0839250886691717</v>
+        <v>0.08662957041997429</v>
       </c>
       <c r="O84" s="104" t="n">
         <v>0.0611152139</v>
@@ -7788,10 +7788,10 @@
         </is>
       </c>
       <c r="C86" s="18" t="n">
-        <v>1.85</v>
+        <v>1.772727272727273</v>
       </c>
       <c r="D86" s="104" t="n">
-        <v>0.7567567567567568</v>
+        <v>0.7692307692307692</v>
       </c>
       <c r="E86" s="104" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v/>
       </c>
       <c r="N86" s="104" t="n">
-        <v>0.2456140350877193</v>
+        <v>0.2295081967213115</v>
       </c>
       <c r="O86" s="104" t="n">
         <v>0.0611152139</v>
@@ -7847,13 +7847,13 @@
         </is>
       </c>
       <c r="C87" s="18" t="n">
-        <v>96.3</v>
+        <v>96.54545454545455</v>
       </c>
       <c r="D87" s="104" t="n">
-        <v>0.3795430944963655</v>
+        <v>0.3799435028248588</v>
       </c>
       <c r="E87" s="104" t="n">
-        <v>0.834858</v>
+        <v>0.836784</v>
       </c>
       <c r="F87" s="104" t="n">
         <v>0.8087257009</v>
@@ -7863,7 +7863,7 @@
         <v/>
       </c>
       <c r="H87" s="104" t="n">
-        <v>0.787304</v>
+        <v>0.786184</v>
       </c>
       <c r="I87" s="104" t="n">
         <v>0.8207995184</v>
@@ -7883,7 +7883,7 @@
         <v/>
       </c>
       <c r="N87" s="104" t="n">
-        <v>0.0167714884696017</v>
+        <v>0.0157823129251701</v>
       </c>
       <c r="O87" s="104" t="n">
         <v>0.0611152139</v>
@@ -10779,10 +10779,10 @@
         </is>
       </c>
       <c r="C149" s="116" t="n">
-        <v>0.2064424084151716</v>
+        <v>0.2056574404662959</v>
       </c>
       <c r="D149" s="116" t="n">
-        <v>0.332475</v>
+        <v>0.331837</v>
       </c>
       <c r="E149" s="20">
         <f>D149/C149</f>
@@ -10800,10 +10800,10 @@
         <v/>
       </c>
       <c r="I149" s="106" t="n">
-        <v>7707249.476190476</v>
+        <v>7668654.636363637</v>
       </c>
       <c r="J149" s="106" t="n">
-        <v>1467249.25156</v>
+        <v>1455233.708801</v>
       </c>
       <c r="K149" s="13" t="inlineStr">
         <is>
@@ -10818,10 +10818,10 @@
         </is>
       </c>
       <c r="C150" s="116" t="n">
-        <v>0.00673394578260548</v>
+        <v>0.006769477479549126</v>
       </c>
       <c r="D150" s="116" t="n">
-        <v>0.02802774511698452</v>
+        <v>0.02799087293035355</v>
       </c>
       <c r="E150" s="20">
         <f>D150/C150</f>
@@ -10839,10 +10839,10 @@
         <v/>
       </c>
       <c r="I150" s="106" t="n">
-        <v>7351980</v>
+        <v>7738094</v>
       </c>
       <c r="J150" s="106" t="n">
-        <v>3749215.65042</v>
+        <v>3900708.87635</v>
       </c>
     </row>
     <row r="152" ht="13.5" customHeight="1">

--- a/dist/downloads/精品货价监控指标_Sheet1.xlsx
+++ b/dist/downloads/精品货价监控指标_Sheet1.xlsx
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="C1" s="11" t="n">
-        <v>46226</v>
+        <v>46229</v>
       </c>
       <c r="D1" s="11" t="inlineStr">
         <is>
@@ -1845,28 +1845,28 @@
         <v>71810000</v>
       </c>
       <c r="D6" s="103" t="n">
-        <v>47525575.17379998</v>
+        <v>54735893.93229</v>
       </c>
       <c r="E6" s="104">
         <f>D6/C6</f>
         <v/>
       </c>
       <c r="F6" s="103" t="n">
-        <v>46784690.49070001</v>
+        <v>52759033.71797</v>
       </c>
       <c r="G6" s="104">
         <f>D6/F6-1</f>
         <v/>
       </c>
       <c r="H6" s="103" t="n">
-        <v>51040630.3491071</v>
+        <v>57963753.57885889</v>
       </c>
       <c r="I6" s="104">
         <f>D6/H6</f>
         <v/>
       </c>
       <c r="J6" s="103" t="n">
-        <v>50900000</v>
+        <v>58000000</v>
       </c>
       <c r="K6" s="104">
         <f>D6/J6</f>
@@ -1884,28 +1884,28 @@
         <v>132000000</v>
       </c>
       <c r="D7" s="103" t="n">
-        <v>67149527.50237</v>
+        <v>76061236.11712998</v>
       </c>
       <c r="E7" s="104">
         <f>D7/C7</f>
         <v/>
       </c>
       <c r="F7" s="103" t="n">
-        <v>76362319.94632</v>
+        <v>84967378.18013997</v>
       </c>
       <c r="G7" s="104">
         <f>D7/F7-1</f>
         <v/>
       </c>
       <c r="H7" s="103" t="n">
-        <v>93822075.00462522</v>
+        <v>106548050.0265892</v>
       </c>
       <c r="I7" s="104">
         <f>D7/H7</f>
         <v/>
       </c>
       <c r="J7" s="103" t="n">
-        <v>95784903.69999999</v>
+        <v>106576302.6</v>
       </c>
       <c r="K7" s="104">
         <f>D7/J7</f>
@@ -1923,28 +1923,28 @@
         <v>9437018</v>
       </c>
       <c r="D8" s="103" t="n">
-        <v>7852956.128949999</v>
+        <v>8807212.498960001</v>
       </c>
       <c r="E8" s="104">
         <f>D8/C8</f>
         <v/>
       </c>
       <c r="F8" s="103" t="n">
-        <v>5373553.104139999</v>
+        <v>5856652.913499999</v>
       </c>
       <c r="G8" s="104">
         <f>D8/F8-1</f>
         <v/>
       </c>
       <c r="H8" s="103" t="n">
-        <v>6707580.383454532</v>
+        <v>7617392.923983509</v>
       </c>
       <c r="I8" s="104">
         <f>D8/H8</f>
         <v/>
       </c>
       <c r="J8" s="103" t="n">
-        <v>6717018.15389968</v>
+        <v>7737018.15389968</v>
       </c>
       <c r="K8" s="104">
         <f>D8/J8</f>
@@ -1962,28 +1962,28 @@
         <v>88000000</v>
       </c>
       <c r="D9" s="103" t="n">
-        <v>59910928.16398</v>
+        <v>67122608.46252</v>
       </c>
       <c r="E9" s="104">
         <f>D9/C9</f>
         <v/>
       </c>
       <c r="F9" s="103" t="n">
-        <v>52905814.67994001</v>
+        <v>59023804.94531002</v>
       </c>
       <c r="G9" s="104">
         <f>D9/F9-1</f>
         <v/>
       </c>
       <c r="H9" s="103" t="n">
-        <v>62548050.00308348</v>
+        <v>71032033.3510595</v>
       </c>
       <c r="I9" s="104">
         <f>D9/H9</f>
         <v/>
       </c>
       <c r="J9" s="103" t="n">
-        <v>64104255</v>
+        <v>71753046</v>
       </c>
       <c r="K9" s="104">
         <f>D9/J9</f>
@@ -2001,28 +2001,28 @@
         <v>66000000</v>
       </c>
       <c r="D10" s="103" t="n">
-        <v>42452329.48069</v>
+        <v>49268004.31358999</v>
       </c>
       <c r="E10" s="104">
         <f>D10/C10</f>
         <v/>
       </c>
       <c r="F10" s="103" t="n">
-        <v>40679482.70381999</v>
+        <v>44587547.41755999</v>
       </c>
       <c r="G10" s="104">
         <f>D10/F10-1</f>
         <v/>
       </c>
       <c r="H10" s="103" t="n">
-        <v>46911037.50231261</v>
+        <v>53274025.01329462</v>
       </c>
       <c r="I10" s="104">
         <f>D10/H10</f>
         <v/>
       </c>
       <c r="J10" s="103" t="n">
-        <v>47200000</v>
+        <v>54300000</v>
       </c>
       <c r="K10" s="104">
         <f>D10/J10</f>
@@ -2040,28 +2040,28 @@
         <v>62390797</v>
       </c>
       <c r="D11" s="103" t="n">
-        <v>33202502.2384</v>
+        <v>37541787.8267</v>
       </c>
       <c r="E11" s="104">
         <f>D11/C11</f>
         <v/>
       </c>
       <c r="F11" s="103" t="n">
-        <v>38581436.85924</v>
+        <v>43771413.76890001</v>
       </c>
       <c r="G11" s="104">
         <f>D11/F11-1</f>
         <v/>
       </c>
       <c r="H11" s="103" t="n">
-        <v>44345712.39191172</v>
+        <v>50360740.60571799</v>
       </c>
       <c r="I11" s="104">
         <f>D11/H11</f>
         <v/>
       </c>
       <c r="J11" s="103" t="n">
-        <v>45509154.67000001</v>
+        <v>51078450.14000002</v>
       </c>
       <c r="K11" s="104">
         <f>D11/J11</f>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="C46" s="107" t="n">
-        <v>116.47248</v>
+        <v>116.445</v>
       </c>
       <c r="D46" s="108" t="n">
         <v>120</v>
@@ -3952,31 +3952,31 @@
         <v>0</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>0.970604</v>
+        <v>0.970375</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>0.029396</v>
+        <v>0.029625</v>
       </c>
       <c r="H46" s="104" t="n">
-        <v>0.790282</v>
+        <v>0.792167</v>
       </c>
       <c r="I46" s="104" t="n">
-        <v>0.83053</v>
+        <v>0.837401</v>
       </c>
       <c r="J46" s="14" t="n">
-        <v>-4.0248</v>
+        <v>-4.5234</v>
       </c>
       <c r="K46" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L46" s="104" t="n">
-        <v>0.981855</v>
+        <v>0.983659</v>
       </c>
       <c r="M46" s="104" t="n">
-        <v>0.8612299999999999</v>
+        <v>0.8681009999999999</v>
       </c>
       <c r="N46" s="14" t="n">
-        <v>12.06250000000001</v>
+        <v>11.5558</v>
       </c>
       <c r="O46" s="14" t="n">
         <v>-2</v>
@@ -3999,31 +3999,31 @@
         <v>0</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>0.548767</v>
+        <v>0.546643</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>0.451233</v>
+        <v>0.453357</v>
       </c>
       <c r="H47" s="104" t="n">
-        <v>0.857147</v>
+        <v>0.8603150000000001</v>
       </c>
       <c r="I47" s="104" t="n">
-        <v>0.8485</v>
+        <v>0.846844</v>
       </c>
       <c r="J47" s="14" t="n">
-        <v>0.8647</v>
+        <v>1.3471</v>
       </c>
       <c r="K47" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L47" s="104" t="n">
-        <v>0.950507</v>
+        <v>0.9500960000000001</v>
       </c>
       <c r="M47" s="104" t="n">
-        <v>0.8791999999999999</v>
+        <v>0.8775439999999999</v>
       </c>
       <c r="N47" s="14" t="n">
-        <v>7.130700000000019</v>
+        <v>7.255200000000016</v>
       </c>
       <c r="O47" s="14" t="n">
         <v>-2</v>
@@ -4037,40 +4037,40 @@
         </is>
       </c>
       <c r="C48" s="107" t="n">
-        <v>110.34237613</v>
+        <v>120</v>
       </c>
       <c r="D48" s="108" t="n">
-        <v>109.466</v>
+        <v>120</v>
       </c>
       <c r="E48" s="108" t="n">
         <v>120</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>0.916805</v>
+        <v>0.91769</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>0.08319500000000001</v>
+        <v>0.08230999999999999</v>
       </c>
       <c r="H48" s="104" t="n">
-        <v>0.753354</v>
+        <v>0.747212</v>
       </c>
       <c r="I48" s="104" t="n">
-        <v>0.778087</v>
+        <v>0.77783</v>
       </c>
       <c r="J48" s="14" t="n">
-        <v>-2.4733</v>
+        <v>-3.0618</v>
       </c>
       <c r="K48" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L48" s="104" t="n">
-        <v>0.736253</v>
+        <v>0.7315</v>
       </c>
       <c r="M48" s="104" t="n">
-        <v>0.8087869999999999</v>
+        <v>0.80853</v>
       </c>
       <c r="N48" s="14" t="n">
-        <v>-7.253399999999999</v>
+        <v>-7.702999999999989</v>
       </c>
       <c r="O48" s="14" t="n">
         <v>-2</v>
@@ -4084,40 +4084,40 @@
         </is>
       </c>
       <c r="C49" s="107" t="n">
-        <v>89.945364064</v>
+        <v>88.3721412</v>
       </c>
       <c r="D49" s="108" t="n">
-        <v>102.944</v>
+        <v>100.916</v>
       </c>
       <c r="E49" s="108" t="n">
         <v>0</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>0.873731</v>
+        <v>0.8757</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>0.126269</v>
+        <v>0.1243</v>
       </c>
       <c r="H49" s="104" t="n">
-        <v>0.808609</v>
+        <v>0.809462</v>
       </c>
       <c r="I49" s="104" t="n">
-        <v>0.830081</v>
+        <v>0.82992</v>
       </c>
       <c r="J49" s="14" t="n">
-        <v>-2.1472</v>
+        <v>-2.0458</v>
       </c>
       <c r="K49" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L49" s="104" t="n">
-        <v>0.870567</v>
+        <v>0.869747</v>
       </c>
       <c r="M49" s="104" t="n">
-        <v>0.8607809999999999</v>
+        <v>0.8606199999999999</v>
       </c>
       <c r="N49" s="14" t="n">
-        <v>0.9786000000000143</v>
+        <v>0.912700000000001</v>
       </c>
       <c r="O49" s="14" t="n">
         <v>-2</v>
@@ -4140,31 +4140,31 @@
         <v>0</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>0.819897</v>
+        <v>0.8197950000000001</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>0.180103</v>
+        <v>0.180205</v>
       </c>
       <c r="H50" s="104" t="n">
-        <v>0.8876540000000001</v>
+        <v>0.887869</v>
       </c>
       <c r="I50" s="104" t="n">
-        <v>0.8362540000000001</v>
+        <v>0.836189</v>
       </c>
       <c r="J50" s="14" t="n">
-        <v>5.14</v>
+        <v>5.168</v>
       </c>
       <c r="K50" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L50" s="104" t="n">
-        <v>0.886872</v>
+        <v>0.8867350000000001</v>
       </c>
       <c r="M50" s="104" t="n">
-        <v>0.8669539999999999</v>
+        <v>0.8668889999999999</v>
       </c>
       <c r="N50" s="14" t="n">
-        <v>1.991800000000012</v>
+        <v>1.984600000000015</v>
       </c>
       <c r="O50" s="14" t="n">
         <v>-2</v>
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="C69" s="10" t="n">
-        <v>0.9383307347157092</v>
+        <v>0.9400249378581307</v>
       </c>
       <c r="D69" s="10" t="n">
-        <v>0.92959908861528</v>
+        <v>0.9279819424053481</v>
       </c>
       <c r="E69" s="10">
         <f>D69-C69</f>
@@ -6886,10 +6886,10 @@
         </is>
       </c>
       <c r="C70" s="10" t="n">
-        <v>0.9324869092347707</v>
+        <v>0.9307705605273685</v>
       </c>
       <c r="D70" s="10" t="n">
-        <v>0.8893768496515304</v>
+        <v>0.8890346641582334</v>
       </c>
       <c r="E70" s="10">
         <f>D70-C70</f>
@@ -6975,10 +6975,10 @@
         </is>
       </c>
       <c r="C71" s="10" t="n">
-        <v>0.925484107726843</v>
+        <v>0.9233301685310997</v>
       </c>
       <c r="D71" s="10" t="n">
-        <v>0.8903021331892945</v>
+        <v>0.8912813922486551</v>
       </c>
       <c r="E71" s="10">
         <f>D71-C71</f>
@@ -7064,10 +7064,10 @@
         </is>
       </c>
       <c r="C72" s="10" t="n">
-        <v>0.976732113881141</v>
+        <v>0.9787141069107258</v>
       </c>
       <c r="D72" s="10" t="n">
-        <v>0.8759961244614934</v>
+        <v>0.8791324787668708</v>
       </c>
       <c r="E72" s="10">
         <f>D72-C72</f>
@@ -7153,10 +7153,10 @@
         </is>
       </c>
       <c r="C73" s="10" t="n">
-        <v>0.9436485456006595</v>
+        <v>0.945126033063153</v>
       </c>
       <c r="D73" s="10" t="n">
-        <v>0.832181997564462</v>
+        <v>0.82895538490589</v>
       </c>
       <c r="E73" s="10">
         <f>D73-C73</f>
@@ -7242,10 +7242,10 @@
         </is>
       </c>
       <c r="C74" s="10" t="n">
-        <v>0.9408606658083472</v>
+        <v>0.9405040502356217</v>
       </c>
       <c r="D74" s="10" t="n">
-        <v>0.879219019959161</v>
+        <v>0.8795221304927711</v>
       </c>
       <c r="E74" s="10">
         <f>D74-C74</f>
@@ -7331,10 +7331,10 @@
         </is>
       </c>
       <c r="C75" s="10" t="n">
-        <v>0.9365345017520862</v>
+        <v>0.9354874739169118</v>
       </c>
       <c r="D75" s="10" t="n">
-        <v>0.8844618193862247</v>
+        <v>0.8845984761544614</v>
       </c>
       <c r="E75" s="10">
         <f>D75-C75</f>
@@ -7517,13 +7517,13 @@
         </is>
       </c>
       <c r="C81" s="18" t="n">
-        <v>1412.272727272727</v>
+        <v>1408.52</v>
       </c>
       <c r="D81" s="104" t="n">
-        <v>0.7101383971676859</v>
+        <v>0.7095958878823162</v>
       </c>
       <c r="E81" s="104" t="n">
-        <v>0.894188</v>
+        <v>0.894176</v>
       </c>
       <c r="F81" s="104" t="n">
         <v>0.8146325152</v>
@@ -7533,7 +7533,7 @@
         <v/>
       </c>
       <c r="H81" s="104" t="n">
-        <v>0.885545</v>
+        <v>0.885266</v>
       </c>
       <c r="I81" s="104" t="n">
         <v>0.8207995184</v>
@@ -7543,7 +7543,7 @@
         <v/>
       </c>
       <c r="K81" s="104" t="n">
-        <v>0.8211143695014663</v>
+        <v>0.8283378746594005</v>
       </c>
       <c r="L81" s="104" t="n">
         <v>0.8082191781</v>
@@ -7553,7 +7553,7 @@
         <v/>
       </c>
       <c r="N81" s="104" t="n">
-        <v>0.073307413862448</v>
+        <v>0.074526339061877</v>
       </c>
       <c r="O81" s="104" t="n">
         <v>0.0611152139</v>
@@ -7570,13 +7570,13 @@
         </is>
       </c>
       <c r="C82" s="18" t="n">
-        <v>116.5909090909091</v>
+        <v>116.8</v>
       </c>
       <c r="D82" s="104" t="n">
-        <v>0.2514619883040936</v>
+        <v>0.2503424657534247</v>
       </c>
       <c r="E82" s="104" t="n">
-        <v>0.729693</v>
+        <v>0.731436</v>
       </c>
       <c r="F82" s="104" t="n">
         <v>0.7556221149</v>
@@ -7608,7 +7608,7 @@
         <v/>
       </c>
       <c r="N82" s="104" t="n">
-        <v>0.1486902927580894</v>
+        <v>0.1481985044187627</v>
       </c>
       <c r="O82" s="104" t="n">
         <v>0.0611152139</v>
@@ -7625,13 +7625,13 @@
         </is>
       </c>
       <c r="C83" s="18" t="n">
-        <v>319.3181818181818</v>
+        <v>316.12</v>
       </c>
       <c r="D83" s="104" t="n">
-        <v>0.7117437722419929</v>
+        <v>0.7089712767303556</v>
       </c>
       <c r="E83" s="104" t="n">
-        <v>0.883387</v>
+        <v>0.882393</v>
       </c>
       <c r="F83" s="104" t="n">
         <v>0.8066</v>
@@ -7641,7 +7641,7 @@
         <v/>
       </c>
       <c r="H83" s="104" t="n">
-        <v>0.8843569999999999</v>
+        <v>0.88357</v>
       </c>
       <c r="I83" s="104" t="n">
         <v>0.8207995184</v>
@@ -7651,7 +7651,7 @@
         <v/>
       </c>
       <c r="K83" s="104" t="n">
-        <v>0.9491525423728814</v>
+        <v>0.9523809523809524</v>
       </c>
       <c r="L83" s="104" t="n">
         <v>0.8082191781</v>
@@ -7661,7 +7661,7 @@
         <v/>
       </c>
       <c r="N83" s="104" t="n">
-        <v>0.0509589282955574</v>
+        <v>0.0477760119292876</v>
       </c>
       <c r="O83" s="104" t="n">
         <v>0.0611152139</v>
@@ -7678,13 +7678,13 @@
         </is>
       </c>
       <c r="C84" s="18" t="n">
-        <v>877.5909090909091</v>
+        <v>876.72</v>
       </c>
       <c r="D84" s="104" t="n">
-        <v>0.8066504376650956</v>
+        <v>0.8070535632813213</v>
       </c>
       <c r="E84" s="104" t="n">
-        <v>0.914772</v>
+        <v>0.916081</v>
       </c>
       <c r="F84" s="104" t="n">
         <v>0.8078</v>
@@ -7694,7 +7694,7 @@
         <v/>
       </c>
       <c r="H84" s="104" t="n">
-        <v>0.89377</v>
+        <v>0.896254</v>
       </c>
       <c r="I84" s="104" t="n">
         <v>0.8207995184</v>
@@ -7704,7 +7704,7 @@
         <v/>
       </c>
       <c r="K84" s="104" t="n">
-        <v>0.7970479704797048</v>
+        <v>0.8054607508532423</v>
       </c>
       <c r="L84" s="104" t="n">
         <v>0.8082191781</v>
@@ -7714,7 +7714,7 @@
         <v/>
       </c>
       <c r="N84" s="104" t="n">
-        <v>0.08662957041997429</v>
+        <v>0.0891388851887284</v>
       </c>
       <c r="O84" s="104" t="n">
         <v>0.0611152139</v>
@@ -7788,10 +7788,10 @@
         </is>
       </c>
       <c r="C86" s="18" t="n">
-        <v>1.772727272727273</v>
+        <v>1.68</v>
       </c>
       <c r="D86" s="104" t="n">
-        <v>0.7692307692307692</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="E86" s="104" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v/>
       </c>
       <c r="N86" s="104" t="n">
-        <v>0.2295081967213115</v>
+        <v>0.208955223880597</v>
       </c>
       <c r="O86" s="104" t="n">
         <v>0.0611152139</v>
@@ -7847,13 +7847,13 @@
         </is>
       </c>
       <c r="C87" s="18" t="n">
-        <v>96.54545454545455</v>
+        <v>96.8</v>
       </c>
       <c r="D87" s="104" t="n">
-        <v>0.3799435028248588</v>
+        <v>0.381404958677686</v>
       </c>
       <c r="E87" s="104" t="n">
-        <v>0.836784</v>
+        <v>0.847162</v>
       </c>
       <c r="F87" s="104" t="n">
         <v>0.8087257009</v>
@@ -7863,7 +7863,7 @@
         <v/>
       </c>
       <c r="H87" s="104" t="n">
-        <v>0.786184</v>
+        <v>0.789895</v>
       </c>
       <c r="I87" s="104" t="n">
         <v>0.8207995184</v>
@@ -7883,7 +7883,7 @@
         <v/>
       </c>
       <c r="N87" s="104" t="n">
-        <v>0.0157823129251701</v>
+        <v>0.0181731229076997</v>
       </c>
       <c r="O87" s="104" t="n">
         <v>0.0611152139</v>
@@ -7973,7 +7973,7 @@
         <v>0</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E94" s="4" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
         <v>0</v>
       </c>
       <c r="D95" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E95" s="4" t="n">
         <v>0</v>
@@ -10779,10 +10779,10 @@
         </is>
       </c>
       <c r="C149" s="116" t="n">
-        <v>0.2056574404662959</v>
+        <v>0.2033793401415985</v>
       </c>
       <c r="D149" s="116" t="n">
-        <v>0.331837</v>
+        <v>0.331626</v>
       </c>
       <c r="E149" s="20">
         <f>D149/C149</f>
@@ -10800,10 +10800,10 @@
         <v/>
       </c>
       <c r="I149" s="106" t="n">
-        <v>7668654.636363637</v>
+        <v>7621041.6</v>
       </c>
       <c r="J149" s="106" t="n">
-        <v>1455233.708801</v>
+        <v>1463091.527252</v>
       </c>
       <c r="K149" s="13" t="inlineStr">
         <is>
@@ -10818,10 +10818,10 @@
         </is>
       </c>
       <c r="C150" s="116" t="n">
-        <v>0.006769477479549126</v>
+        <v>0.007090098790202326</v>
       </c>
       <c r="D150" s="116" t="n">
-        <v>0.02799087293035355</v>
+        <v>0.02881851247498287</v>
       </c>
       <c r="E150" s="20">
         <f>D150/C150</f>
@@ -10839,10 +10839,10 @@
         <v/>
       </c>
       <c r="I150" s="106" t="n">
-        <v>7738094</v>
+        <v>9252265</v>
       </c>
       <c r="J150" s="106" t="n">
-        <v>3900708.87635</v>
+        <v>4576725.16585</v>
       </c>
     </row>
     <row r="152" ht="13.5" customHeight="1">

--- a/dist/downloads/精品货价监控指标_Sheet1.xlsx
+++ b/dist/downloads/精品货价监控指标_Sheet1.xlsx
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="C1" s="11" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="D1" s="11" t="inlineStr">
         <is>
@@ -1845,28 +1845,28 @@
         <v>71810000</v>
       </c>
       <c r="D6" s="103" t="n">
-        <v>54735893.93229</v>
+        <v>56999284.90107001</v>
       </c>
       <c r="E6" s="104">
         <f>D6/C6</f>
         <v/>
       </c>
       <c r="F6" s="103" t="n">
-        <v>52759033.71797</v>
+        <v>55034458.62962</v>
       </c>
       <c r="G6" s="104">
         <f>D6/F6-1</f>
         <v/>
       </c>
       <c r="H6" s="103" t="n">
-        <v>57963753.57885889</v>
+        <v>60271461.32210948</v>
       </c>
       <c r="I6" s="104">
         <f>D6/H6</f>
         <v/>
       </c>
       <c r="J6" s="103" t="n">
-        <v>58000000</v>
+        <v>60500000</v>
       </c>
       <c r="K6" s="104">
         <f>D6/J6</f>
@@ -1884,28 +1884,28 @@
         <v>132000000</v>
       </c>
       <c r="D7" s="103" t="n">
-        <v>76061236.11712998</v>
+        <v>79575002.75239</v>
       </c>
       <c r="E7" s="104">
         <f>D7/C7</f>
         <v/>
       </c>
       <c r="F7" s="103" t="n">
-        <v>84967378.18013997</v>
+        <v>88621756.21001998</v>
       </c>
       <c r="G7" s="104">
         <f>D7/F7-1</f>
         <v/>
       </c>
       <c r="H7" s="103" t="n">
-        <v>106548050.0265892</v>
+        <v>110790041.7005772</v>
       </c>
       <c r="I7" s="104">
         <f>D7/H7</f>
         <v/>
       </c>
       <c r="J7" s="103" t="n">
-        <v>106576302.6</v>
+        <v>111158802.7</v>
       </c>
       <c r="K7" s="104">
         <f>D7/J7</f>
@@ -1923,28 +1923,28 @@
         <v>9437018</v>
       </c>
       <c r="D8" s="103" t="n">
-        <v>8807212.498960001</v>
+        <v>9133109.288960002</v>
       </c>
       <c r="E8" s="104">
         <f>D8/C8</f>
         <v/>
       </c>
       <c r="F8" s="103" t="n">
-        <v>5856652.913499999</v>
+        <v>6257675.0648</v>
       </c>
       <c r="G8" s="104">
         <f>D8/F8-1</f>
         <v/>
       </c>
       <c r="H8" s="103" t="n">
-        <v>7617392.923983509</v>
+        <v>7920663.770826501</v>
       </c>
       <c r="I8" s="104">
         <f>D8/H8</f>
         <v/>
       </c>
       <c r="J8" s="103" t="n">
-        <v>7737018.15389968</v>
+        <v>7997018.15389968</v>
       </c>
       <c r="K8" s="104">
         <f>D8/J8</f>
@@ -1962,28 +1962,28 @@
         <v>88000000</v>
       </c>
       <c r="D9" s="103" t="n">
-        <v>67122608.46252</v>
+        <v>69431574.30306</v>
       </c>
       <c r="E9" s="104">
         <f>D9/C9</f>
         <v/>
       </c>
       <c r="F9" s="103" t="n">
-        <v>59023804.94531002</v>
+        <v>60801537.63507</v>
       </c>
       <c r="G9" s="104">
         <f>D9/F9-1</f>
         <v/>
       </c>
       <c r="H9" s="103" t="n">
-        <v>71032033.3510595</v>
+        <v>73860027.80038483</v>
       </c>
       <c r="I9" s="104">
         <f>D9/H9</f>
         <v/>
       </c>
       <c r="J9" s="103" t="n">
-        <v>71753046</v>
+        <v>74144241</v>
       </c>
       <c r="K9" s="104">
         <f>D9/J9</f>
@@ -2001,28 +2001,28 @@
         <v>66000000</v>
       </c>
       <c r="D10" s="103" t="n">
-        <v>49268004.31358999</v>
+        <v>51610245.77668999</v>
       </c>
       <c r="E10" s="104">
         <f>D10/C10</f>
         <v/>
       </c>
       <c r="F10" s="103" t="n">
-        <v>44587547.41755999</v>
+        <v>45753281.23078001</v>
       </c>
       <c r="G10" s="104">
         <f>D10/F10-1</f>
         <v/>
       </c>
       <c r="H10" s="103" t="n">
-        <v>53274025.01329462</v>
+        <v>55395020.85028862</v>
       </c>
       <c r="I10" s="104">
         <f>D10/H10</f>
         <v/>
       </c>
       <c r="J10" s="103" t="n">
-        <v>54300000</v>
+        <v>56100000</v>
       </c>
       <c r="K10" s="104">
         <f>D10/J10</f>
@@ -2040,28 +2040,28 @@
         <v>62390797</v>
       </c>
       <c r="D11" s="103" t="n">
-        <v>37541787.8267</v>
+        <v>39250344.41577</v>
       </c>
       <c r="E11" s="104">
         <f>D11/C11</f>
         <v/>
       </c>
       <c r="F11" s="103" t="n">
-        <v>43771413.76890001</v>
+        <v>45520419.64603</v>
       </c>
       <c r="G11" s="104">
         <f>D11/F11-1</f>
         <v/>
       </c>
       <c r="H11" s="103" t="n">
-        <v>50360740.60571799</v>
+        <v>52365750.01032007</v>
       </c>
       <c r="I11" s="104">
         <f>D11/H11</f>
         <v/>
       </c>
       <c r="J11" s="103" t="n">
-        <v>51078450.14000002</v>
+        <v>52859416.16000002</v>
       </c>
       <c r="K11" s="104">
         <f>D11/J11</f>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="C46" s="107" t="n">
-        <v>116.445</v>
+        <v>116.38536</v>
       </c>
       <c r="D46" s="108" t="n">
         <v>120</v>
@@ -3952,31 +3952,31 @@
         <v>0</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>0.970375</v>
+        <v>0.969878</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>0.029625</v>
+        <v>0.030122</v>
       </c>
       <c r="H46" s="104" t="n">
-        <v>0.792167</v>
+        <v>0.792257</v>
       </c>
       <c r="I46" s="104" t="n">
-        <v>0.837401</v>
+        <v>0.838044</v>
       </c>
       <c r="J46" s="14" t="n">
-        <v>-4.5234</v>
+        <v>-4.5787</v>
       </c>
       <c r="K46" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L46" s="104" t="n">
-        <v>0.983659</v>
+        <v>0.9810990000000001</v>
       </c>
       <c r="M46" s="104" t="n">
-        <v>0.8681009999999999</v>
+        <v>0.868744</v>
       </c>
       <c r="N46" s="14" t="n">
-        <v>11.5558</v>
+        <v>11.2355</v>
       </c>
       <c r="O46" s="14" t="n">
         <v>-2</v>
@@ -3999,31 +3999,31 @@
         <v>0</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>0.546643</v>
+        <v>0.548602</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>0.453357</v>
+        <v>0.451398</v>
       </c>
       <c r="H47" s="104" t="n">
-        <v>0.8603150000000001</v>
+        <v>0.860413</v>
       </c>
       <c r="I47" s="104" t="n">
-        <v>0.846844</v>
+        <v>0.845364</v>
       </c>
       <c r="J47" s="14" t="n">
-        <v>1.3471</v>
+        <v>1.5049</v>
       </c>
       <c r="K47" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L47" s="104" t="n">
-        <v>0.9500960000000001</v>
+        <v>0.949968</v>
       </c>
       <c r="M47" s="104" t="n">
-        <v>0.8775439999999999</v>
+        <v>0.876064</v>
       </c>
       <c r="N47" s="14" t="n">
-        <v>7.255200000000016</v>
+        <v>7.3904</v>
       </c>
       <c r="O47" s="14" t="n">
         <v>-2</v>
@@ -4046,31 +4046,31 @@
         <v>120</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>0.91769</v>
+        <v>0.917855</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>0.08230999999999999</v>
+        <v>0.082145</v>
       </c>
       <c r="H48" s="104" t="n">
-        <v>0.747212</v>
+        <v>0.745633</v>
       </c>
       <c r="I48" s="104" t="n">
-        <v>0.77783</v>
+        <v>0.776695</v>
       </c>
       <c r="J48" s="14" t="n">
-        <v>-3.0618</v>
+        <v>-3.1062</v>
       </c>
       <c r="K48" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L48" s="104" t="n">
-        <v>0.7315</v>
+        <v>0.729692</v>
       </c>
       <c r="M48" s="104" t="n">
-        <v>0.80853</v>
+        <v>0.807395</v>
       </c>
       <c r="N48" s="14" t="n">
-        <v>-7.702999999999989</v>
+        <v>-7.770299999999992</v>
       </c>
       <c r="O48" s="14" t="n">
         <v>-2</v>
@@ -4084,40 +4084,40 @@
         </is>
       </c>
       <c r="C49" s="107" t="n">
-        <v>88.3721412</v>
+        <v>87.87192760000001</v>
       </c>
       <c r="D49" s="108" t="n">
-        <v>100.916</v>
+        <v>100.37</v>
       </c>
       <c r="E49" s="108" t="n">
         <v>0</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>0.8757</v>
+        <v>0.87548</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>0.1243</v>
+        <v>0.12452</v>
       </c>
       <c r="H49" s="104" t="n">
-        <v>0.809462</v>
+        <v>0.809492</v>
       </c>
       <c r="I49" s="104" t="n">
-        <v>0.82992</v>
+        <v>0.829677</v>
       </c>
       <c r="J49" s="14" t="n">
-        <v>-2.0458</v>
+        <v>-2.0185</v>
       </c>
       <c r="K49" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L49" s="104" t="n">
-        <v>0.869747</v>
+        <v>0.86995</v>
       </c>
       <c r="M49" s="104" t="n">
-        <v>0.8606199999999999</v>
+        <v>0.8603769999999998</v>
       </c>
       <c r="N49" s="14" t="n">
-        <v>0.912700000000001</v>
+        <v>0.9573000000000178</v>
       </c>
       <c r="O49" s="14" t="n">
         <v>-2</v>
@@ -4140,31 +4140,31 @@
         <v>0</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>0.8197950000000001</v>
+        <v>0.819715</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>0.180205</v>
+        <v>0.180285</v>
       </c>
       <c r="H50" s="104" t="n">
-        <v>0.887869</v>
+        <v>0.887647</v>
       </c>
       <c r="I50" s="104" t="n">
-        <v>0.836189</v>
+        <v>0.835376</v>
       </c>
       <c r="J50" s="14" t="n">
-        <v>5.168</v>
+        <v>5.2271</v>
       </c>
       <c r="K50" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L50" s="104" t="n">
-        <v>0.8867350000000001</v>
+        <v>0.886501</v>
       </c>
       <c r="M50" s="104" t="n">
-        <v>0.8668889999999999</v>
+        <v>0.866076</v>
       </c>
       <c r="N50" s="14" t="n">
-        <v>1.984600000000015</v>
+        <v>2.042500000000004</v>
       </c>
       <c r="O50" s="14" t="n">
         <v>-2</v>
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="C69" s="10" t="n">
-        <v>0.9400249378581307</v>
+        <v>0.9397703933271144</v>
       </c>
       <c r="D69" s="10" t="n">
-        <v>0.9279819424053481</v>
+        <v>0.9279951388178347</v>
       </c>
       <c r="E69" s="10">
         <f>D69-C69</f>
@@ -6886,10 +6886,10 @@
         </is>
       </c>
       <c r="C70" s="10" t="n">
-        <v>0.9307705605273685</v>
+        <v>0.9301326499269785</v>
       </c>
       <c r="D70" s="10" t="n">
-        <v>0.8890346641582334</v>
+        <v>0.8892783347494847</v>
       </c>
       <c r="E70" s="10">
         <f>D70-C70</f>
@@ -6975,10 +6975,10 @@
         </is>
       </c>
       <c r="C71" s="10" t="n">
-        <v>0.9233301685310997</v>
+        <v>0.922493958562407</v>
       </c>
       <c r="D71" s="10" t="n">
-        <v>0.8912813922486551</v>
+        <v>0.8914821215654777</v>
       </c>
       <c r="E71" s="10">
         <f>D71-C71</f>
@@ -7064,10 +7064,10 @@
         </is>
       </c>
       <c r="C72" s="10" t="n">
-        <v>0.9787141069107258</v>
+        <v>0.9792712353493512</v>
       </c>
       <c r="D72" s="10" t="n">
-        <v>0.8791324787668708</v>
+        <v>0.8798879221523218</v>
       </c>
       <c r="E72" s="10">
         <f>D72-C72</f>
@@ -7153,10 +7153,10 @@
         </is>
       </c>
       <c r="C73" s="10" t="n">
-        <v>0.945126033063153</v>
+        <v>0.9459716828904183</v>
       </c>
       <c r="D73" s="10" t="n">
-        <v>0.82895538490589</v>
+        <v>0.8280673271363532</v>
       </c>
       <c r="E73" s="10">
         <f>D73-C73</f>
@@ -7242,10 +7242,10 @@
         </is>
       </c>
       <c r="C74" s="10" t="n">
-        <v>0.9405040502356217</v>
+        <v>0.9405248187055548</v>
       </c>
       <c r="D74" s="10" t="n">
-        <v>0.8795221304927711</v>
+        <v>0.8791349788351291</v>
       </c>
       <c r="E74" s="10">
         <f>D74-C74</f>
@@ -7331,10 +7331,10 @@
         </is>
       </c>
       <c r="C75" s="10" t="n">
-        <v>0.9354874739169118</v>
+        <v>0.935103817094359</v>
       </c>
       <c r="D75" s="10" t="n">
-        <v>0.8845984761544614</v>
+        <v>0.884673920460158</v>
       </c>
       <c r="E75" s="10">
         <f>D75-C75</f>
@@ -10779,10 +10779,10 @@
         </is>
       </c>
       <c r="C149" s="116" t="n">
-        <v>0.2033793401415985</v>
+        <v>0.202850597971508</v>
       </c>
       <c r="D149" s="116" t="n">
-        <v>0.331626</v>
+        <v>0.330816</v>
       </c>
       <c r="E149" s="20">
         <f>D149/C149</f>
@@ -10800,10 +10800,10 @@
         <v/>
       </c>
       <c r="I149" s="106" t="n">
-        <v>7621041.6</v>
+        <v>7638431.961538462</v>
       </c>
       <c r="J149" s="106" t="n">
-        <v>1463091.527252</v>
+        <v>1461772.405828</v>
       </c>
       <c r="K149" s="13" t="inlineStr">
         <is>
@@ -10818,10 +10818,10 @@
         </is>
       </c>
       <c r="C150" s="116" t="n">
-        <v>0.007090098790202326</v>
+        <v>0.007127555721542105</v>
       </c>
       <c r="D150" s="116" t="n">
-        <v>0.02881851247498287</v>
+        <v>0.02857905115243414</v>
       </c>
       <c r="E150" s="20">
         <f>D150/C150</f>
@@ -10839,10 +10839,10 @@
         <v/>
       </c>
       <c r="I150" s="106" t="n">
-        <v>9252265</v>
+        <v>9720331</v>
       </c>
       <c r="J150" s="106" t="n">
-        <v>4576725.16585</v>
+        <v>4738720.92434</v>
       </c>
     </row>
     <row r="152" ht="13.5" customHeight="1">

--- a/dist/downloads/精品货价监控指标_Sheet1.xlsx
+++ b/dist/downloads/精品货价监控指标_Sheet1.xlsx
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="C1" s="11" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="D1" s="11" t="inlineStr">
         <is>
@@ -1845,28 +1845,28 @@
         <v>71810000</v>
       </c>
       <c r="D6" s="103" t="n">
-        <v>56999284.90107001</v>
+        <v>59282290.94605001</v>
       </c>
       <c r="E6" s="104">
         <f>D6/C6</f>
         <v/>
       </c>
       <c r="F6" s="103" t="n">
-        <v>55034458.62962</v>
+        <v>57053880.82841</v>
       </c>
       <c r="G6" s="104">
         <f>D6/F6-1</f>
         <v/>
       </c>
       <c r="H6" s="103" t="n">
-        <v>60271461.32210948</v>
+        <v>62579169.06536008</v>
       </c>
       <c r="I6" s="104">
         <f>D6/H6</f>
         <v/>
       </c>
       <c r="J6" s="103" t="n">
-        <v>60500000</v>
+        <v>62600000</v>
       </c>
       <c r="K6" s="104">
         <f>D6/J6</f>
@@ -1884,28 +1884,28 @@
         <v>132000000</v>
       </c>
       <c r="D7" s="103" t="n">
-        <v>79575002.75239</v>
+        <v>82216567.05815001</v>
       </c>
       <c r="E7" s="104">
         <f>D7/C7</f>
         <v/>
       </c>
       <c r="F7" s="103" t="n">
-        <v>88621756.21001998</v>
+        <v>91704524.86462997</v>
       </c>
       <c r="G7" s="104">
         <f>D7/F7-1</f>
         <v/>
       </c>
       <c r="H7" s="103" t="n">
-        <v>110790041.7005772</v>
+        <v>115032033.3745652</v>
       </c>
       <c r="I7" s="104">
         <f>D7/H7</f>
         <v/>
       </c>
       <c r="J7" s="103" t="n">
-        <v>111158802.7</v>
+        <v>115026097</v>
       </c>
       <c r="K7" s="104">
         <f>D7/J7</f>
@@ -1923,28 +1923,28 @@
         <v>9437018</v>
       </c>
       <c r="D8" s="103" t="n">
-        <v>9133109.288960002</v>
+        <v>9352880.30896</v>
       </c>
       <c r="E8" s="104">
         <f>D8/C8</f>
         <v/>
       </c>
       <c r="F8" s="103" t="n">
-        <v>6257675.0648</v>
+        <v>6429613.647990001</v>
       </c>
       <c r="G8" s="104">
         <f>D8/F8-1</f>
         <v/>
       </c>
       <c r="H8" s="103" t="n">
-        <v>7920663.770826501</v>
+        <v>8223934.617669493</v>
       </c>
       <c r="I8" s="104">
         <f>D8/H8</f>
         <v/>
       </c>
       <c r="J8" s="103" t="n">
-        <v>7997018.15389968</v>
+        <v>8257018.15389968</v>
       </c>
       <c r="K8" s="104">
         <f>D8/J8</f>
@@ -1962,28 +1962,28 @@
         <v>88000000</v>
       </c>
       <c r="D9" s="103" t="n">
-        <v>69431574.30306</v>
+        <v>72595270.08000998</v>
       </c>
       <c r="E9" s="104">
         <f>D9/C9</f>
         <v/>
       </c>
       <c r="F9" s="103" t="n">
-        <v>60801537.63507</v>
+        <v>63877686.13121</v>
       </c>
       <c r="G9" s="104">
         <f>D9/F9-1</f>
         <v/>
       </c>
       <c r="H9" s="103" t="n">
-        <v>73860027.80038483</v>
+        <v>76688022.24971017</v>
       </c>
       <c r="I9" s="104">
         <f>D9/H9</f>
         <v/>
       </c>
       <c r="J9" s="103" t="n">
-        <v>74144241</v>
+        <v>77541457</v>
       </c>
       <c r="K9" s="104">
         <f>D9/J9</f>
@@ -2001,28 +2001,28 @@
         <v>66000000</v>
       </c>
       <c r="D10" s="103" t="n">
-        <v>51610245.77668999</v>
+        <v>53355811.23975999</v>
       </c>
       <c r="E10" s="104">
         <f>D10/C10</f>
         <v/>
       </c>
       <c r="F10" s="103" t="n">
-        <v>45753281.23078001</v>
+        <v>47343676.45017999</v>
       </c>
       <c r="G10" s="104">
         <f>D10/F10-1</f>
         <v/>
       </c>
       <c r="H10" s="103" t="n">
-        <v>55395020.85028862</v>
+        <v>57516016.68728262</v>
       </c>
       <c r="I10" s="104">
         <f>D10/H10</f>
         <v/>
       </c>
       <c r="J10" s="103" t="n">
-        <v>56100000</v>
+        <v>57900000</v>
       </c>
       <c r="K10" s="104">
         <f>D10/J10</f>
@@ -2040,28 +2040,28 @@
         <v>62390797</v>
       </c>
       <c r="D11" s="103" t="n">
-        <v>39250344.41577</v>
+        <v>40718302.81533001</v>
       </c>
       <c r="E11" s="104">
         <f>D11/C11</f>
         <v/>
       </c>
       <c r="F11" s="103" t="n">
-        <v>45520419.64603</v>
+        <v>47251904.58927</v>
       </c>
       <c r="G11" s="104">
         <f>D11/F11-1</f>
         <v/>
       </c>
       <c r="H11" s="103" t="n">
-        <v>52365750.01032007</v>
+        <v>54370759.41492216</v>
       </c>
       <c r="I11" s="104">
         <f>D11/H11</f>
         <v/>
       </c>
       <c r="J11" s="103" t="n">
-        <v>52859416.16000002</v>
+        <v>54654650.90000002</v>
       </c>
       <c r="K11" s="104">
         <f>D11/J11</f>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="C46" s="107" t="n">
-        <v>116.38536</v>
+        <v>116.37252</v>
       </c>
       <c r="D46" s="108" t="n">
         <v>120</v>
@@ -3952,31 +3952,31 @@
         <v>0</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>0.969878</v>
+        <v>0.969771</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>0.030122</v>
+        <v>0.030229</v>
       </c>
       <c r="H46" s="104" t="n">
-        <v>0.792257</v>
+        <v>0.793679</v>
       </c>
       <c r="I46" s="104" t="n">
-        <v>0.838044</v>
+        <v>0.840204</v>
       </c>
       <c r="J46" s="14" t="n">
-        <v>-4.5787</v>
+        <v>-4.6525</v>
       </c>
       <c r="K46" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L46" s="104" t="n">
-        <v>0.9810990000000001</v>
+        <v>0.981531</v>
       </c>
       <c r="M46" s="104" t="n">
-        <v>0.868744</v>
+        <v>0.8709039999999999</v>
       </c>
       <c r="N46" s="14" t="n">
-        <v>11.2355</v>
+        <v>11.06270000000001</v>
       </c>
       <c r="O46" s="14" t="n">
         <v>-2</v>
@@ -3999,31 +3999,31 @@
         <v>0</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>0.548602</v>
+        <v>0.552836</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>0.451398</v>
+        <v>0.447164</v>
       </c>
       <c r="H47" s="104" t="n">
-        <v>0.860413</v>
+        <v>0.862525</v>
       </c>
       <c r="I47" s="104" t="n">
-        <v>0.845364</v>
+        <v>0.844747</v>
       </c>
       <c r="J47" s="14" t="n">
-        <v>1.5049</v>
+        <v>1.7778</v>
       </c>
       <c r="K47" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L47" s="104" t="n">
-        <v>0.949968</v>
+        <v>0.949715</v>
       </c>
       <c r="M47" s="104" t="n">
-        <v>0.876064</v>
+        <v>0.8754469999999999</v>
       </c>
       <c r="N47" s="14" t="n">
-        <v>7.3904</v>
+        <v>7.426800000000014</v>
       </c>
       <c r="O47" s="14" t="n">
         <v>-2</v>
@@ -4046,31 +4046,31 @@
         <v>120</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>0.917855</v>
+        <v>0.918307</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>0.082145</v>
+        <v>0.081693</v>
       </c>
       <c r="H48" s="104" t="n">
-        <v>0.745633</v>
+        <v>0.7451410000000001</v>
       </c>
       <c r="I48" s="104" t="n">
-        <v>0.776695</v>
+        <v>0.776822</v>
       </c>
       <c r="J48" s="14" t="n">
-        <v>-3.1062</v>
+        <v>-3.1681</v>
       </c>
       <c r="K48" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L48" s="104" t="n">
-        <v>0.729692</v>
+        <v>0.727641</v>
       </c>
       <c r="M48" s="104" t="n">
-        <v>0.807395</v>
+        <v>0.8075219999999999</v>
       </c>
       <c r="N48" s="14" t="n">
-        <v>-7.770299999999992</v>
+        <v>-7.988099999999989</v>
       </c>
       <c r="O48" s="14" t="n">
         <v>-2</v>
@@ -4084,40 +4084,40 @@
         </is>
       </c>
       <c r="C49" s="107" t="n">
-        <v>87.87192760000001</v>
+        <v>87.086004192</v>
       </c>
       <c r="D49" s="108" t="n">
-        <v>100.37</v>
+        <v>99.396</v>
       </c>
       <c r="E49" s="108" t="n">
         <v>0</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>0.87548</v>
+        <v>0.876152</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>0.12452</v>
+        <v>0.123848</v>
       </c>
       <c r="H49" s="104" t="n">
-        <v>0.809492</v>
+        <v>0.809742</v>
       </c>
       <c r="I49" s="104" t="n">
-        <v>0.829677</v>
+        <v>0.82944</v>
       </c>
       <c r="J49" s="14" t="n">
-        <v>-2.0185</v>
+        <v>-1.9698</v>
       </c>
       <c r="K49" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L49" s="104" t="n">
-        <v>0.86995</v>
+        <v>0.869915</v>
       </c>
       <c r="M49" s="104" t="n">
-        <v>0.8603769999999998</v>
+        <v>0.8601399999999999</v>
       </c>
       <c r="N49" s="14" t="n">
-        <v>0.9573000000000178</v>
+        <v>0.9775000000000063</v>
       </c>
       <c r="O49" s="14" t="n">
         <v>-2</v>
@@ -4140,31 +4140,31 @@
         <v>0</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>0.819715</v>
+        <v>0.819269</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>0.180285</v>
+        <v>0.180731</v>
       </c>
       <c r="H50" s="104" t="n">
-        <v>0.887647</v>
+        <v>0.888065</v>
       </c>
       <c r="I50" s="104" t="n">
-        <v>0.835376</v>
+        <v>0.8355320000000001</v>
       </c>
       <c r="J50" s="14" t="n">
-        <v>5.2271</v>
+        <v>5.2533</v>
       </c>
       <c r="K50" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L50" s="104" t="n">
-        <v>0.886501</v>
+        <v>0.886522</v>
       </c>
       <c r="M50" s="104" t="n">
-        <v>0.866076</v>
+        <v>0.866232</v>
       </c>
       <c r="N50" s="14" t="n">
-        <v>2.042500000000004</v>
+        <v>2.028999999999996</v>
       </c>
       <c r="O50" s="14" t="n">
         <v>-2</v>
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="C69" s="10" t="n">
-        <v>0.9397703933271144</v>
+        <v>0.9400170376200739</v>
       </c>
       <c r="D69" s="10" t="n">
-        <v>0.9279951388178347</v>
+        <v>0.9278937175607233</v>
       </c>
       <c r="E69" s="10">
         <f>D69-C69</f>
@@ -6886,10 +6886,10 @@
         </is>
       </c>
       <c r="C70" s="10" t="n">
-        <v>0.9301326499269785</v>
+        <v>0.9295969216394627</v>
       </c>
       <c r="D70" s="10" t="n">
-        <v>0.8892783347494847</v>
+        <v>0.8888186180667089</v>
       </c>
       <c r="E70" s="10">
         <f>D70-C70</f>
@@ -6975,10 +6975,10 @@
         </is>
       </c>
       <c r="C71" s="10" t="n">
-        <v>0.922493958562407</v>
+        <v>0.9219400076214633</v>
       </c>
       <c r="D71" s="10" t="n">
-        <v>0.8914821215654777</v>
+        <v>0.8912389392578917</v>
       </c>
       <c r="E71" s="10">
         <f>D71-C71</f>
@@ -7064,10 +7064,10 @@
         </is>
       </c>
       <c r="C72" s="10" t="n">
-        <v>0.9792712353493512</v>
+        <v>0.9795473206723364</v>
       </c>
       <c r="D72" s="10" t="n">
-        <v>0.8798879221523218</v>
+        <v>0.8805529419547967</v>
       </c>
       <c r="E72" s="10">
         <f>D72-C72</f>
@@ -7153,10 +7153,10 @@
         </is>
       </c>
       <c r="C73" s="10" t="n">
-        <v>0.9459716828904183</v>
+        <v>0.9444891078667765</v>
       </c>
       <c r="D73" s="10" t="n">
-        <v>0.8280673271363532</v>
+        <v>0.8272107325994765</v>
       </c>
       <c r="E73" s="10">
         <f>D73-C73</f>
@@ -7242,10 +7242,10 @@
         </is>
       </c>
       <c r="C74" s="10" t="n">
-        <v>0.9405248187055548</v>
+        <v>0.9397490986296675</v>
       </c>
       <c r="D74" s="10" t="n">
-        <v>0.8791349788351291</v>
+        <v>0.8790686129160361</v>
       </c>
       <c r="E74" s="10">
         <f>D74-C74</f>
@@ -7331,10 +7331,10 @@
         </is>
       </c>
       <c r="C75" s="10" t="n">
-        <v>0.935103817094359</v>
+        <v>0.9345430954304992</v>
       </c>
       <c r="D75" s="10" t="n">
-        <v>0.884673920460158</v>
+        <v>0.8844281210841539</v>
       </c>
       <c r="E75" s="10">
         <f>D75-C75</f>
@@ -10779,10 +10779,10 @@
         </is>
       </c>
       <c r="C149" s="116" t="n">
-        <v>0.202850597971508</v>
+        <v>0.2025752109475947</v>
       </c>
       <c r="D149" s="116" t="n">
-        <v>0.330816</v>
+        <v>0.330517</v>
       </c>
       <c r="E149" s="20">
         <f>D149/C149</f>
@@ -10800,10 +10800,10 @@
         <v/>
       </c>
       <c r="I149" s="106" t="n">
-        <v>7638431.961538462</v>
+        <v>7636188.037037037</v>
       </c>
       <c r="J149" s="106" t="n">
-        <v>1461772.405828</v>
+        <v>1458008.503465</v>
       </c>
       <c r="K149" s="13" t="inlineStr">
         <is>
@@ -10818,10 +10818,10 @@
         </is>
       </c>
       <c r="C150" s="116" t="n">
-        <v>0.007127555721542105</v>
+        <v>0.007295338151612621</v>
       </c>
       <c r="D150" s="116" t="n">
-        <v>0.02857905115243414</v>
+        <v>0.02866368692945488</v>
       </c>
       <c r="E150" s="20">
         <f>D150/C150</f>
@@ -10839,10 +10839,10 @@
         <v/>
       </c>
       <c r="I150" s="106" t="n">
-        <v>9720331</v>
+        <v>10340122</v>
       </c>
       <c r="J150" s="106" t="n">
-        <v>4738720.92434</v>
+        <v>4918687.94053</v>
       </c>
     </row>
     <row r="152" ht="13.5" customHeight="1">
